--- a/results/peru/figures/tornado_summary.xlsx
+++ b/results/peru/figures/tornado_summary.xlsx
@@ -435,10 +435,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="39" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
     <col width="90" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -462,7 +462,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Assess how uncertainty in generation-plant delays, transmission delays and fuel prices affects transmission expansion, generation capacity and the country average price.</t>
+          <t>Assess how uncertainty in generation project delays, transmission project delays, fuel prices, demand growth affects transmission expansion, generation capacity and the country average price.</t>
         </is>
       </c>
     </row>
@@ -474,31 +474,31 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>ModeloCh4_Correccion.mdl with data from PERU.xlsx; simulated 2025-01 to 2050-01 (300 months, dt = 0.25 month) with PySD.</t>
+          <t>ModeloCh4_Correccion.mdl with data from PERU.xlsx, patched with the 4 sensitivity constants and published as ModeloCh4_Sens2.vpmx; simulated 2025-01 to 2050-01 (300 months, dt = 0.25 month) with the Vensim DSS DLL.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Factor 1 – Generation delays</t>
+          <t>Factor 1 – Generation project delays</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>±20% of licensing + construction time of every technology (same mechanism as 'Other delays' in sheet 'Gen Investment parameters'). Base = 0 %.</t>
+          <t>±20%. Licensing + construction time of every technology, through the same mechanism as 'Other delays' in sheet 'Gen Investment parameters'. Expressed against the workbook base case (B15 = -0.2), not the planned time.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Factor 2 – Transmission delays</t>
+          <t>Factor 2 – Transmission project delays</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>±20% on the public-tender, investor-selection, licensing and construction times of transmission projects (lines and GETs, sheet 'Trans Investment parameters'). The 12-month planning cycle is not changed.</t>
+          <t>±20%. Public-tender, investor-selection, licensing and construction times of transmission projects (lines and GETs, sheet 'Trans Investment parameters'). The 12-month planning cycle is deliberately not changed.</t>
         </is>
       </c>
     </row>
@@ -510,149 +510,161 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>±15% on 'Fuel Cost' of every technology (sheet 'Gen Investment parameters', row 21).</t>
+          <t>±15%. 'Fuel Cost' of every technology that burns fuel (sheet 'Gen Investment parameters', row 21).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Tornado diagram</t>
+          <t>Factor 4 – Demand growth</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>One-at-a-time: each factor is set to its low and its high value while the others stay at base. Bars show the change of the KPI against the base case; factors are sorted by swing (|high − low|).</t>
+          <t>±20%. The 2050 demand level reached by the growth path. The multiplier is 1 in January 2025 and 1 + factor in January 2050, so the starting point is untouched and only the growth rate varies.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P10–P90 distribution</t>
+          <t>Tornado diagram</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>34 Latin-Hypercube Monte Carlo runs with the three factors varying simultaneously (uniform distributions). P10 = value exceeded by 90 % of runs; P90 = value exceeded by 10 % of runs; P50 = median.</t>
+          <t>One-at-a-time: each factor is set to its low and its high value while the others stay at base. Bars show the change of the KPI against the base case; factors are sorted by swing (|high − low|).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Best / worst scenario</t>
+          <t>P10–P90 distribution</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Chosen among the Monte Carlo runs: best = lowest country average price, worst = highest country average price</t>
+          <t>120 Latin-Hypercube Monte Carlo runs with all 4 factors varying simultaneously (uniform distributions). P10 = value exceeded by 90 % of runs; P90 = value exceeded by 10 % of runs; P50 = median.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>KPI – Total transmission [km]</t>
+          <t>Best / worst scenario</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>'Total Transmission' = demand-connection + generation-connection + interconnection lines, value at Jan-2050.</t>
+          <t>Chosen among the Monte Carlo runs: best = lowest country average price, worst = highest country average price</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>KPI – Transmission capacity [GW]</t>
+          <t>KPI – Total transmission [km]</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>'Total Interconnection Capacity' (MW) / 1000, value at Jan-2050.</t>
+          <t>'Total Transmission' = demand-connection + generation-connection + interconnection lines, value at Jan-2050.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>KPI – Generation capacity [GW]</t>
+          <t>KPI – Transmission capacity [GW]</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>'Total Generation Capacity', value at Jan-2050.</t>
+          <t>'Total Interconnection Capacity' (MW) / 1000, value at Jan-2050.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>KPI – Country average price [USD/MWh]</t>
+          <t>KPI – Generation capacity [GW]</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Mean of 'Electricity Tariff[Regulated, Zone]' over the active zones; KPI = mean of the last 12 months of the run. Components: generation tariff, transmission tariff, congestion tariff and other charges (taxes, distribution, etc.).</t>
+          <t>'Total Generation Capacity', value at Jan-2050.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sampling</t>
+          <t>KPI – Country average price [USD/MWh]</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Latin Hypercube (seed 2026): each factor range is cut into 34 equal intervals and one value is drawn at random inside each interval; the intervals of the three factors are paired at random. This covers each range evenly with fewer runs than plain random sampling.</t>
+          <t>Mean of 'Electricity Tariff[Regulated, Zone]' over the active zones; KPI = mean of the last 12 months of the run. Components: generation tariff, transmission tariff, congestion tariff and other charges (taxes, distribution, etc.).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Convergence check</t>
+          <t>Sampling</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Sheet 'Convergence' and chart 10: P10/P50/P90 recomputed with the first 10, 20, 50, 100 ... runs. If the values no longer move, the number of runs is sufficient.</t>
+          <t>Latin Hypercube (seed 2026): each factor range is cut into 120 equal intervals and one value is drawn at random inside each interval; the intervals of the three factors are paired at random. This covers each range evenly with fewer runs than plain random sampling.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Factor influence</t>
+          <t>Convergence check</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Sheet 'Rank_correlation' and chart 11: Spearman rank correlation between each factor and each KPI over all Monte Carlo runs (-1 to +1; near 0 = no influence). It complements the tornado, which varies one factor at a time.</t>
+          <t>Sheet 'Convergence' and chart 10: P10/P50/P90 recomputed with the first 10, 20, 50, 100 ... runs. If the values no longer move, the number of runs is sufficient.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Traceability</t>
+          <t>Factor influence</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>tornado_results/runs/&lt;run&gt;.csv = full monthly output of every run; &lt;run&gt;.json = factor values used; run_log.csv = finish time and duration of each run; experiment_design.csv = full sample. Model copy actually simulated: tornado_results/_model/peru_sens.mdl.</t>
+          <t>Sheet 'Rank_correlation' and chart 11: Spearman rank correlation between each factor and each KPI over all Monte Carlo runs (-1 to +1; near 0 = no influence). It complements the tornado, which varies one factor at a time.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>Traceability</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>tornado_results/runs/&lt;run&gt;.csv = full monthly output of every run; &lt;run&gt;.json = factor values used; run_log.csv = finish time and duration of each run; experiment_design.csv = full sample. Model copy actually simulated: tornado_results/_model/peru_sens.mdl.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>Charts</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>00 summary table, 01–02 P10–P90 distribution, 03 tornado, 04 price, 05 installed capacity by technology, 06 generation by technology, 07 transmission capacity (GW), 08 transmission length (km), 09 sampling design, 10 convergence, 11 factor influence.</t>
         </is>
@@ -669,30 +681,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U4"/>
+  <dimension ref="A1:V4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
-    <col width="39" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
     <col width="39" customWidth="1" min="10" max="10"/>
     <col width="39" customWidth="1" min="11" max="11"/>
-    <col width="47" customWidth="1" min="12" max="12"/>
+    <col width="39" customWidth="1" min="12" max="12"/>
     <col width="47" customWidth="1" min="13" max="13"/>
     <col width="47" customWidth="1" min="14" max="14"/>
-    <col width="50" customWidth="1" min="15" max="15"/>
+    <col width="47" customWidth="1" min="15" max="15"/>
     <col width="50" customWidth="1" min="16" max="16"/>
     <col width="50" customWidth="1" min="17" max="17"/>
-    <col width="37" customWidth="1" min="18" max="18"/>
-    <col width="46" customWidth="1" min="19" max="19"/>
-    <col width="54" customWidth="1" min="20" max="20"/>
-    <col width="52" customWidth="1" min="21" max="21"/>
+    <col width="50" customWidth="1" min="18" max="18"/>
+    <col width="37" customWidth="1" min="19" max="19"/>
+    <col width="46" customWidth="1" min="20" max="20"/>
+    <col width="54" customWidth="1" min="21" max="21"/>
+    <col width="52" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -708,12 +721,12 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Generation delays</t>
+          <t>Generation project delays</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Transmission delays</t>
+          <t>Transmission project delays</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -723,80 +736,85 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Demand growth</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Total transmission 2030 [km]</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Total transmission 2040 [km]</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Total transmission 2050 [km]</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Total transmission capacity 2030 [GW]</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Total transmission capacity 2040 [GW]</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Total transmission capacity 2050 [GW]</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Total installed generation capacity 2030 [GW]</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Total installed generation capacity 2040 [GW]</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Total installed generation capacity 2050 [GW]</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Country average electricity price 2030 [USD/MWh]</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Country average electricity price 2040 [USD/MWh]</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Country average electricity price 2050 [USD/MWh]</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Total transmission 2050 vs base [%]</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Total transmission capacity 2050 vs base [%]</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Total installed generation capacity 2050 vs base [%]</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Country average electricity price 2050 vs base [%]</t>
         </is>
@@ -828,44 +846,46 @@
           <t>+0.0%</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>20896.26</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>33462.76</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>46341.23</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>1.6</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>3.56</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>4.56</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>21.26</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>39.99</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>63.85</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>191.83</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>147.2</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>124.46</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -876,6 +896,9 @@
       <c r="U2" t="n">
         <v>0</v>
       </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -885,71 +908,76 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>mc_012</t>
+          <t>mc_009</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+15.7%</t>
+          <t>+9.8%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+5.2%</t>
+          <t>+2.6%</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>+14.2%</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>20198.84</v>
+          <t>-2.5%</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>+17.3%</t>
+        </is>
       </c>
       <c r="G3" t="n">
-        <v>34320.48</v>
+        <v>20695.17</v>
       </c>
       <c r="H3" t="n">
-        <v>48817.38</v>
+        <v>37885.32</v>
       </c>
       <c r="I3" t="n">
+        <v>58561.73</v>
+      </c>
+      <c r="J3" t="n">
         <v>1.6</v>
       </c>
-      <c r="J3" t="n">
-        <v>3.67</v>
-      </c>
       <c r="K3" t="n">
-        <v>4.62</v>
+        <v>3.75</v>
       </c>
       <c r="L3" t="n">
-        <v>19.81</v>
+        <v>5.03</v>
       </c>
       <c r="M3" t="n">
-        <v>41.45</v>
+        <v>20.15</v>
       </c>
       <c r="N3" t="n">
-        <v>68.68000000000001</v>
+        <v>47.9</v>
       </c>
       <c r="O3" t="n">
-        <v>198.82</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>135.7</v>
+        <v>204.31</v>
       </c>
       <c r="Q3" t="n">
-        <v>116.53</v>
+        <v>135.44</v>
       </c>
       <c r="R3" t="n">
-        <v>5.3</v>
+        <v>114.94</v>
       </c>
       <c r="S3" t="n">
-        <v>1.3</v>
+        <v>26.4</v>
       </c>
       <c r="T3" t="n">
-        <v>7.6</v>
+        <v>10.3</v>
       </c>
       <c r="U3" t="n">
-        <v>-6.4</v>
+        <v>35.3</v>
+      </c>
+      <c r="V3" t="n">
+        <v>-7.6</v>
       </c>
     </row>
     <row r="4">
@@ -960,71 +988,76 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mc_001</t>
+          <t>mc_058</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-8.9%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>+8.2%</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-7.0%</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>21084.35</v>
+          <t>-1.1%</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>-16.5%</t>
+        </is>
       </c>
       <c r="G4" t="n">
-        <v>35267.86</v>
+        <v>20480.54</v>
       </c>
       <c r="H4" t="n">
-        <v>47605.65</v>
+        <v>31015.11</v>
       </c>
       <c r="I4" t="n">
+        <v>38927.13</v>
+      </c>
+      <c r="J4" t="n">
         <v>1.6</v>
       </c>
-      <c r="J4" t="n">
-        <v>3.52</v>
-      </c>
       <c r="K4" t="n">
-        <v>4.51</v>
+        <v>3.37</v>
       </c>
       <c r="L4" t="n">
-        <v>21.96</v>
+        <v>4.34</v>
       </c>
       <c r="M4" t="n">
-        <v>43.78</v>
+        <v>21.11</v>
       </c>
       <c r="N4" t="n">
-        <v>64.38</v>
+        <v>36.6</v>
       </c>
       <c r="O4" t="n">
-        <v>182.76</v>
+        <v>49.18</v>
       </c>
       <c r="P4" t="n">
-        <v>136.97</v>
+        <v>186.01</v>
       </c>
       <c r="Q4" t="n">
-        <v>130.18</v>
+        <v>143.02</v>
       </c>
       <c r="R4" t="n">
-        <v>2.7</v>
+        <v>135.63</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.1</v>
+        <v>-16</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8</v>
+        <v>-4.8</v>
       </c>
       <c r="U4" t="n">
-        <v>4.6</v>
+        <v>-23</v>
+      </c>
+      <c r="V4" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1105,25 +1138,25 @@
         <v>46341.23</v>
       </c>
       <c r="C2" t="n">
-        <v>46884.53</v>
+        <v>39857.99</v>
       </c>
       <c r="D2" t="n">
-        <v>48851.79</v>
+        <v>47787.91</v>
       </c>
       <c r="E2" t="n">
-        <v>49533.3</v>
+        <v>57068.7</v>
       </c>
       <c r="F2" t="n">
-        <v>48547.66</v>
+        <v>48422.22</v>
       </c>
       <c r="G2" t="n">
-        <v>46073.64</v>
+        <v>37658.21</v>
       </c>
       <c r="H2" t="n">
-        <v>50755.98</v>
+        <v>60509.77</v>
       </c>
       <c r="I2" t="n">
-        <v>2648.77</v>
+        <v>17210.7</v>
       </c>
     </row>
     <row r="3">
@@ -1136,25 +1169,25 @@
         <v>4.56</v>
       </c>
       <c r="C3" t="n">
-        <v>4.42</v>
+        <v>4.23</v>
       </c>
       <c r="D3" t="n">
-        <v>4.61</v>
+        <v>4.7</v>
       </c>
       <c r="E3" t="n">
-        <v>4.86</v>
+        <v>5.29</v>
       </c>
       <c r="F3" t="n">
-        <v>4.64</v>
+        <v>4.73</v>
       </c>
       <c r="G3" t="n">
-        <v>4.35</v>
+        <v>4.02</v>
       </c>
       <c r="H3" t="n">
-        <v>5.26</v>
+        <v>5.84</v>
       </c>
       <c r="I3" t="n">
-        <v>0.44</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="4">
@@ -1167,25 +1200,25 @@
         <v>63.85</v>
       </c>
       <c r="C4" t="n">
-        <v>64.18000000000001</v>
+        <v>52.33</v>
       </c>
       <c r="D4" t="n">
-        <v>68.63</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>70.45999999999999</v>
+        <v>82.48999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>68.01000000000001</v>
+        <v>67.38</v>
       </c>
       <c r="G4" t="n">
-        <v>62.58</v>
+        <v>47.81</v>
       </c>
       <c r="H4" t="n">
-        <v>73.54000000000001</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>6.28</v>
+        <v>30.16</v>
       </c>
     </row>
     <row r="5">
@@ -1198,25 +1231,25 @@
         <v>124.46</v>
       </c>
       <c r="C5" t="n">
-        <v>116.79</v>
+        <v>116.83</v>
       </c>
       <c r="D5" t="n">
-        <v>119.41</v>
+        <v>122.76</v>
       </c>
       <c r="E5" t="n">
-        <v>125.78</v>
+        <v>129.42</v>
       </c>
       <c r="F5" t="n">
-        <v>120.66</v>
+        <v>122.89</v>
       </c>
       <c r="G5" t="n">
-        <v>116.53</v>
+        <v>114.94</v>
       </c>
       <c r="H5" t="n">
-        <v>130.18</v>
+        <v>135.63</v>
       </c>
       <c r="I5" t="n">
-        <v>8.99</v>
+        <v>12.59</v>
       </c>
     </row>
   </sheetData>
@@ -1230,7 +1263,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -1322,7 +1355,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Generation project delays</t>
+          <t>Demand growth</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1334,25 +1367,25 @@
         <v>124.463</v>
       </c>
       <c r="F2" t="n">
-        <v>118.6</v>
+        <v>131.308</v>
       </c>
       <c r="G2" t="n">
-        <v>124.122</v>
+        <v>118.222</v>
       </c>
       <c r="H2" t="n">
-        <v>-5.863</v>
+        <v>6.845</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.34</v>
+        <v>-6.241</v>
       </c>
       <c r="J2" t="n">
-        <v>-4.711</v>
+        <v>5.5</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.273</v>
+        <v>-5.014</v>
       </c>
       <c r="L2" t="n">
-        <v>5.523</v>
+        <v>13.086</v>
       </c>
     </row>
     <row r="3">
@@ -1368,7 +1401,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Transmission project delays</t>
+          <t>Generation project delays</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1380,25 +1413,25 @@
         <v>124.463</v>
       </c>
       <c r="F3" t="n">
-        <v>123.102</v>
+        <v>118.6</v>
       </c>
       <c r="G3" t="n">
-        <v>125.729</v>
+        <v>124.122</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.36</v>
+        <v>-5.863</v>
       </c>
       <c r="I3" t="n">
-        <v>1.266</v>
+        <v>-0.34</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.093</v>
+        <v>-4.711</v>
       </c>
       <c r="K3" t="n">
-        <v>1.017</v>
+        <v>-0.273</v>
       </c>
       <c r="L3" t="n">
-        <v>2.626</v>
+        <v>5.523</v>
       </c>
     </row>
     <row r="4">
@@ -1414,83 +1447,83 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Fuel prices</t>
+          <t>Transmission project delays</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>−15% / +15%</t>
+          <t>−20% / +20%</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>124.463</v>
       </c>
       <c r="F4" t="n">
-        <v>124.96</v>
+        <v>123.102</v>
       </c>
       <c r="G4" t="n">
-        <v>124.954</v>
+        <v>125.729</v>
       </c>
       <c r="H4" t="n">
-        <v>0.497</v>
+        <v>-1.36</v>
       </c>
       <c r="I4" t="n">
-        <v>0.492</v>
+        <v>1.266</v>
       </c>
       <c r="J4" t="n">
-        <v>0.399</v>
+        <v>-1.093</v>
       </c>
       <c r="K4" t="n">
-        <v>0.395</v>
+        <v>1.017</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005</v>
+        <v>2.626</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Total installed generation capacity</t>
+          <t>Country average electricity price</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>USD/MWh</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Generation project delays</t>
+          <t>Fuel prices</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>−20% / +20%</t>
+          <t>−15% / +15%</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>63.85</v>
+        <v>124.463</v>
       </c>
       <c r="F5" t="n">
-        <v>70.63800000000001</v>
+        <v>124.96</v>
       </c>
       <c r="G5" t="n">
-        <v>64.553</v>
+        <v>124.954</v>
       </c>
       <c r="H5" t="n">
-        <v>6.788</v>
+        <v>0.497</v>
       </c>
       <c r="I5" t="n">
-        <v>0.704</v>
+        <v>0.492</v>
       </c>
       <c r="J5" t="n">
-        <v>10.631</v>
+        <v>0.399</v>
       </c>
       <c r="K5" t="n">
-        <v>1.102</v>
+        <v>0.395</v>
       </c>
       <c r="L5" t="n">
-        <v>6.085</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="6">
@@ -1506,37 +1539,37 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fuel prices</t>
+          <t>Demand growth</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>−15% / +15%</t>
+          <t>−20% / +20%</t>
         </is>
       </c>
       <c r="E6" t="n">
         <v>63.85</v>
       </c>
       <c r="F6" t="n">
-        <v>64.078</v>
+        <v>48.499</v>
       </c>
       <c r="G6" t="n">
-        <v>64.718</v>
+        <v>82.578</v>
       </c>
       <c r="H6" t="n">
-        <v>0.229</v>
+        <v>-15.351</v>
       </c>
       <c r="I6" t="n">
-        <v>0.868</v>
+        <v>18.728</v>
       </c>
       <c r="J6" t="n">
-        <v>0.358</v>
+        <v>-24.042</v>
       </c>
       <c r="K6" t="n">
-        <v>1.36</v>
+        <v>29.332</v>
       </c>
       <c r="L6" t="n">
-        <v>0.64</v>
+        <v>34.079</v>
       </c>
     </row>
     <row r="7">
@@ -1552,7 +1585,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Transmission project delays</t>
+          <t>Generation project delays</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1564,117 +1597,117 @@
         <v>63.85</v>
       </c>
       <c r="F7" t="n">
-        <v>64.72</v>
+        <v>70.63800000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>64.643</v>
+        <v>64.553</v>
       </c>
       <c r="H7" t="n">
-        <v>0.87</v>
+        <v>6.788</v>
       </c>
       <c r="I7" t="n">
-        <v>0.794</v>
+        <v>0.704</v>
       </c>
       <c r="J7" t="n">
-        <v>1.363</v>
+        <v>10.631</v>
       </c>
       <c r="K7" t="n">
-        <v>1.243</v>
+        <v>1.102</v>
       </c>
       <c r="L7" t="n">
-        <v>0.076</v>
+        <v>6.085</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total transmission</t>
+          <t>Total installed generation capacity</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>km</t>
+          <t>GW</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Generation project delays</t>
+          <t>Fuel prices</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>−20% / +20%</t>
+          <t>−15% / +15%</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>46341.234</v>
+        <v>63.85</v>
       </c>
       <c r="F8" t="n">
-        <v>49317.469</v>
+        <v>64.078</v>
       </c>
       <c r="G8" t="n">
-        <v>47107.207</v>
+        <v>64.718</v>
       </c>
       <c r="H8" t="n">
-        <v>2976.234</v>
+        <v>0.229</v>
       </c>
       <c r="I8" t="n">
-        <v>765.973</v>
+        <v>0.868</v>
       </c>
       <c r="J8" t="n">
-        <v>6.422</v>
+        <v>0.358</v>
       </c>
       <c r="K8" t="n">
-        <v>1.653</v>
+        <v>1.36</v>
       </c>
       <c r="L8" t="n">
-        <v>2210.262</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Total transmission</t>
+          <t>Total installed generation capacity</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>km</t>
+          <t>GW</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fuel prices</t>
+          <t>Transmission project delays</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>−15% / +15%</t>
+          <t>−20% / +20%</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>46341.234</v>
+        <v>63.85</v>
       </c>
       <c r="F9" t="n">
-        <v>46432.367</v>
+        <v>64.72</v>
       </c>
       <c r="G9" t="n">
-        <v>47161.309</v>
+        <v>64.643</v>
       </c>
       <c r="H9" t="n">
-        <v>91.133</v>
+        <v>0.87</v>
       </c>
       <c r="I9" t="n">
-        <v>820.074</v>
+        <v>0.794</v>
       </c>
       <c r="J9" t="n">
-        <v>0.197</v>
+        <v>1.363</v>
       </c>
       <c r="K9" t="n">
-        <v>1.77</v>
+        <v>1.243</v>
       </c>
       <c r="L9" t="n">
-        <v>728.941</v>
+        <v>0.076</v>
       </c>
     </row>
     <row r="10">
@@ -1690,7 +1723,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Transmission project delays</t>
+          <t>Demand growth</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1702,41 +1735,41 @@
         <v>46341.234</v>
       </c>
       <c r="F10" t="n">
-        <v>47153.531</v>
+        <v>37589.227</v>
       </c>
       <c r="G10" t="n">
-        <v>46666.988</v>
+        <v>57383.387</v>
       </c>
       <c r="H10" t="n">
-        <v>812.297</v>
+        <v>-8752.008</v>
       </c>
       <c r="I10" t="n">
-        <v>325.754</v>
+        <v>11042.152</v>
       </c>
       <c r="J10" t="n">
-        <v>1.753</v>
+        <v>-18.886</v>
       </c>
       <c r="K10" t="n">
-        <v>0.703</v>
+        <v>23.828</v>
       </c>
       <c r="L10" t="n">
-        <v>486.543</v>
+        <v>19794.16</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Total transmission capacity</t>
+          <t>Total transmission</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>km</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Transmission project delays</t>
+          <t>Generation project delays</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1745,39 +1778,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4.556</v>
+        <v>46341.234</v>
       </c>
       <c r="F11" t="n">
-        <v>4.791</v>
+        <v>49317.469</v>
       </c>
       <c r="G11" t="n">
-        <v>4.334</v>
+        <v>47107.207</v>
       </c>
       <c r="H11" t="n">
-        <v>0.235</v>
+        <v>2976.234</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.222</v>
+        <v>765.973</v>
       </c>
       <c r="J11" t="n">
-        <v>5.161</v>
+        <v>6.422</v>
       </c>
       <c r="K11" t="n">
-        <v>-4.878</v>
+        <v>1.653</v>
       </c>
       <c r="L11" t="n">
-        <v>0.457</v>
+        <v>2210.262</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total transmission capacity</t>
+          <t>Total transmission</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>km</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1791,73 +1824,257 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4.556</v>
+        <v>46341.234</v>
       </c>
       <c r="F12" t="n">
-        <v>4.777</v>
+        <v>46432.367</v>
       </c>
       <c r="G12" t="n">
-        <v>4.583</v>
+        <v>47161.309</v>
       </c>
       <c r="H12" t="n">
-        <v>0.221</v>
+        <v>91.133</v>
       </c>
       <c r="I12" t="n">
-        <v>0.027</v>
+        <v>820.074</v>
       </c>
       <c r="J12" t="n">
-        <v>4.852</v>
+        <v>0.197</v>
       </c>
       <c r="K12" t="n">
-        <v>0.591</v>
+        <v>1.77</v>
       </c>
       <c r="L12" t="n">
-        <v>0.194</v>
+        <v>728.941</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Total transmission</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>km</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Transmission project delays</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>−20% / +20%</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>46341.234</v>
+      </c>
+      <c r="F13" t="n">
+        <v>47153.531</v>
+      </c>
+      <c r="G13" t="n">
+        <v>46666.988</v>
+      </c>
+      <c r="H13" t="n">
+        <v>812.297</v>
+      </c>
+      <c r="I13" t="n">
+        <v>325.754</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.753</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.703</v>
+      </c>
+      <c r="L13" t="n">
+        <v>486.543</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>Total transmission capacity</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>GW</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Demand growth</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>−20% / +20%</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4.556</v>
+      </c>
+      <c r="F14" t="n">
+        <v>4.174</v>
+      </c>
+      <c r="G14" t="n">
+        <v>5.255</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0.382</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-8.388</v>
+      </c>
+      <c r="K14" t="n">
+        <v>15.356</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.082</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Total transmission capacity</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>GW</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Transmission project delays</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>−20% / +20%</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4.556</v>
+      </c>
+      <c r="F15" t="n">
+        <v>4.791</v>
+      </c>
+      <c r="G15" t="n">
+        <v>4.334</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-0.222</v>
+      </c>
+      <c r="J15" t="n">
+        <v>5.161</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-4.878</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.457</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Total transmission capacity</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>GW</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Fuel prices</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>−15% / +15%</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>4.556</v>
+      </c>
+      <c r="F16" t="n">
+        <v>4.777</v>
+      </c>
+      <c r="G16" t="n">
+        <v>4.583</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.221</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4.852</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.591</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.194</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Total transmission capacity</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>GW</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>Generation project delays</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>−20% / +20%</t>
         </is>
       </c>
-      <c r="E13" t="n">
+      <c r="E17" t="n">
         <v>4.556</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F17" t="n">
         <v>4.459</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G17" t="n">
         <v>4.36</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H17" t="n">
         <v>-0.097</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I17" t="n">
         <v>-0.196</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J17" t="n">
         <v>-2.138</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K17" t="n">
         <v>-4.305</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L17" t="n">
         <v>0.099</v>
       </c>
     </row>
@@ -1872,18 +2089,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I208"/>
+  <dimension ref="A1:J130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
-    <col width="45" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="42" customWidth="1" min="9" max="9"/>
+    <col width="45" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1899,12 +2117,12 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Generation delays</t>
+          <t>Generation project delays</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Transmission delays</t>
+          <t>Transmission project delays</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -1914,20 +2132,25 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Demand growth</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Total transmission [km]</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Total transmission capacity [GW]</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Total installed generation capacity [GW]</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Country average electricity price [USD/MWh]</t>
         </is>
@@ -1954,15 +2177,18 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
         <v>46341.2344</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>4.5559</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>63.8496</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>124.4627</v>
       </c>
     </row>
@@ -1987,15 +2213,18 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
         <v>49317.4688</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>4.4585</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>70.6377</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>118.5997</v>
       </c>
     </row>
@@ -2020,15 +2249,18 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
         <v>47107.207</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>4.3598</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>64.5532</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>124.1224</v>
       </c>
     </row>
@@ -2053,15 +2285,18 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
         <v>47153.5312</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>4.791</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>64.7196</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>123.1024</v>
       </c>
     </row>
@@ -2086,15 +2321,18 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
         <v>46666.9883</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>4.3337</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>64.6433</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>125.7287</v>
       </c>
     </row>
@@ -2119,15 +2357,18 @@
         <v>-0.15</v>
       </c>
       <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
         <v>46432.3672</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>4.777</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>64.07810000000001</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>124.9597</v>
       </c>
     </row>
@@ -2152,88 +2393,97 @@
         <v>0.15</v>
       </c>
       <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
         <v>47161.3086</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>4.5828</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>64.71769999999999</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>124.9544</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>mc_000</t>
+          <t>oat_demand_low</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>montecarlo</t>
+          <t>tornado</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.1157</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.19</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1346</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>48611.6484</v>
+        <v>-0.2</v>
       </c>
       <c r="G9" t="n">
-        <v>4.6971</v>
+        <v>37589.2266</v>
       </c>
       <c r="H9" t="n">
-        <v>67.8901</v>
+        <v>4.1738</v>
       </c>
       <c r="I9" t="n">
-        <v>123.0365</v>
+        <v>48.4986</v>
+      </c>
+      <c r="J9" t="n">
+        <v>131.3079</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>mc_001</t>
+          <t>oat_demand_high</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>montecarlo</t>
+          <t>tornado</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-0.0891</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0563</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0703</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>47605.6484</v>
+        <v>0.2</v>
       </c>
       <c r="G10" t="n">
-        <v>4.5119</v>
+        <v>57383.3867</v>
       </c>
       <c r="H10" t="n">
-        <v>64.3817</v>
+        <v>5.2555</v>
       </c>
       <c r="I10" t="n">
-        <v>130.1787</v>
+        <v>82.5779</v>
+      </c>
+      <c r="J10" t="n">
+        <v>118.2218</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>mc_002</t>
+          <t>mc_000</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2242,31 +2492,34 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-0.1011</v>
+        <v>-0.1157</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1578</v>
+        <v>-0.19</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1119</v>
+        <v>0.1346</v>
       </c>
       <c r="F11" t="n">
-        <v>50755.9805</v>
+        <v>0.0528</v>
       </c>
       <c r="G11" t="n">
-        <v>4.4017</v>
+        <v>51216.2969</v>
       </c>
       <c r="H11" t="n">
-        <v>73.54179999999999</v>
+        <v>5.2641</v>
       </c>
       <c r="I11" t="n">
-        <v>117.0946</v>
+        <v>71.2602</v>
+      </c>
+      <c r="J11" t="n">
+        <v>124.9816</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>mc_003</t>
+          <t>mc_001</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2275,31 +2528,34 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.035</v>
+        <v>-0.0891</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1114</v>
+        <v>-0.0563</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1296</v>
+        <v>-0.0703</v>
       </c>
       <c r="F12" t="n">
-        <v>49571.0977</v>
+        <v>0.1381</v>
       </c>
       <c r="G12" t="n">
-        <v>4.5487</v>
+        <v>55646.9844</v>
       </c>
       <c r="H12" t="n">
-        <v>70.68519999999999</v>
+        <v>4.9051</v>
       </c>
       <c r="I12" t="n">
-        <v>119.5822</v>
+        <v>80.267</v>
+      </c>
+      <c r="J12" t="n">
+        <v>116.7765</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>mc_004</t>
+          <t>mc_002</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2308,31 +2564,34 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-0.1364</v>
+        <v>-0.1011</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0359</v>
+        <v>0.1578</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.0594</v>
+        <v>-0.1119</v>
       </c>
       <c r="F13" t="n">
-        <v>47794.0352</v>
+        <v>-0.0346</v>
       </c>
       <c r="G13" t="n">
-        <v>4.4884</v>
+        <v>48898.2227</v>
       </c>
       <c r="H13" t="n">
-        <v>67.3309</v>
+        <v>4.272</v>
       </c>
       <c r="I13" t="n">
-        <v>124.3787</v>
+        <v>70.1942</v>
+      </c>
+      <c r="J13" t="n">
+        <v>118.5954</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>mc_005</t>
+          <t>mc_003</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2341,31 +2600,34 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-0.1666</v>
+        <v>0.035</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0139</v>
+        <v>0.1114</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.1365</v>
+        <v>0.1296</v>
       </c>
       <c r="F14" t="n">
-        <v>49255.5625</v>
+        <v>-0.1703</v>
       </c>
       <c r="G14" t="n">
-        <v>4.3929</v>
+        <v>39286.7852</v>
       </c>
       <c r="H14" t="n">
-        <v>70.27549999999999</v>
+        <v>4.252</v>
       </c>
       <c r="I14" t="n">
-        <v>118.7494</v>
+        <v>51.1146</v>
+      </c>
+      <c r="J14" t="n">
+        <v>130.2801</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>mc_006</t>
+          <t>mc_004</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2374,31 +2636,34 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.182</v>
+        <v>-0.1364</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1171</v>
+        <v>0.0359</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1146</v>
+        <v>-0.0594</v>
       </c>
       <c r="F15" t="n">
-        <v>49714.0352</v>
+        <v>-0.0031</v>
       </c>
       <c r="G15" t="n">
-        <v>4.5366</v>
+        <v>47777.4258</v>
       </c>
       <c r="H15" t="n">
-        <v>70.51819999999999</v>
+        <v>4.5545</v>
       </c>
       <c r="I15" t="n">
-        <v>117.6486</v>
+        <v>66.8198</v>
+      </c>
+      <c r="J15" t="n">
+        <v>125.2102</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>mc_007</t>
+          <t>mc_005</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2407,31 +2672,34 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-0.0384</v>
+        <v>-0.1666</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1443</v>
+        <v>0.0139</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0362</v>
+        <v>-0.1365</v>
       </c>
       <c r="F16" t="n">
-        <v>47346.5234</v>
+        <v>-0.058</v>
       </c>
       <c r="G16" t="n">
-        <v>4.893</v>
+        <v>44903.3164</v>
       </c>
       <c r="H16" t="n">
-        <v>64.6036</v>
+        <v>4.4953</v>
       </c>
       <c r="I16" t="n">
-        <v>123.8058</v>
+        <v>60.891</v>
+      </c>
+      <c r="J16" t="n">
+        <v>128.6234</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>mc_008</t>
+          <t>mc_006</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2440,31 +2708,34 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0953</v>
+        <v>0.182</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.08699999999999999</v>
+        <v>0.1171</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0127</v>
+        <v>-0.1146</v>
       </c>
       <c r="F17" t="n">
-        <v>49160.1914</v>
+        <v>0.0559</v>
       </c>
       <c r="G17" t="n">
-        <v>4.6834</v>
+        <v>52477.8164</v>
       </c>
       <c r="H17" t="n">
-        <v>68.53919999999999</v>
+        <v>4.7933</v>
       </c>
       <c r="I17" t="n">
-        <v>118.2202</v>
+        <v>75.9851</v>
+      </c>
+      <c r="J17" t="n">
+        <v>116.1476</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>mc_009</t>
+          <t>mc_007</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2473,31 +2744,34 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0985</v>
+        <v>-0.0384</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0263</v>
+        <v>-0.1443</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0251</v>
+        <v>0.0362</v>
       </c>
       <c r="F18" t="n">
-        <v>49405.8047</v>
+        <v>-0.1252</v>
       </c>
       <c r="G18" t="n">
-        <v>4.9328</v>
+        <v>40717.3203</v>
       </c>
       <c r="H18" t="n">
-        <v>70.7445</v>
+        <v>4.311</v>
       </c>
       <c r="I18" t="n">
-        <v>116.7593</v>
+        <v>53.6482</v>
+      </c>
+      <c r="J18" t="n">
+        <v>126.8422</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>mc_010</t>
+          <t>mc_008</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2506,31 +2780,34 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-0.1404</v>
+        <v>0.0953</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0809</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0075</v>
+        <v>0.0127</v>
       </c>
       <c r="F19" t="n">
-        <v>49047.2891</v>
+        <v>0.0658</v>
       </c>
       <c r="G19" t="n">
-        <v>5.2566</v>
+        <v>51802.5781</v>
       </c>
       <c r="H19" t="n">
-        <v>69.36150000000001</v>
+        <v>4.9401</v>
       </c>
       <c r="I19" t="n">
-        <v>118.5493</v>
+        <v>72.7332</v>
+      </c>
+      <c r="J19" t="n">
+        <v>116.9505</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>mc_011</t>
+          <t>mc_009</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2539,31 +2816,34 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-0.1569</v>
+        <v>0.0985</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1733</v>
+        <v>0.0263</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0437</v>
+        <v>-0.0251</v>
       </c>
       <c r="F20" t="n">
-        <v>48807.7188</v>
+        <v>0.1728</v>
       </c>
       <c r="G20" t="n">
-        <v>4.7795</v>
+        <v>58561.7344</v>
       </c>
       <c r="H20" t="n">
-        <v>69.023</v>
+        <v>5.0258</v>
       </c>
       <c r="I20" t="n">
-        <v>126.082</v>
+        <v>86.3984</v>
+      </c>
+      <c r="J20" t="n">
+        <v>114.9366</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>mc_012</t>
+          <t>mc_010</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2572,31 +2852,34 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.1573</v>
+        <v>-0.1404</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0517</v>
+        <v>-0.0809</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1421</v>
+        <v>0.0075</v>
       </c>
       <c r="F21" t="n">
-        <v>48817.375</v>
+        <v>-0.0375</v>
       </c>
       <c r="G21" t="n">
-        <v>4.6238</v>
+        <v>45875.8164</v>
       </c>
       <c r="H21" t="n">
-        <v>68.6801</v>
+        <v>5.1406</v>
       </c>
       <c r="I21" t="n">
-        <v>116.5298</v>
+        <v>62.2593</v>
+      </c>
+      <c r="J21" t="n">
+        <v>130.3038</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>mc_013</t>
+          <t>mc_011</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2605,31 +2888,34 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.1731</v>
+        <v>-0.1569</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1708</v>
+        <v>0.1733</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.0372</v>
+        <v>0.0437</v>
       </c>
       <c r="F22" t="n">
-        <v>49043.9922</v>
+        <v>0.1918</v>
       </c>
       <c r="G22" t="n">
-        <v>4.634</v>
+        <v>60509.7695</v>
       </c>
       <c r="H22" t="n">
-        <v>68.69370000000001</v>
+        <v>4.976</v>
       </c>
       <c r="I22" t="n">
-        <v>118.3564</v>
+        <v>89.741</v>
+      </c>
+      <c r="J22" t="n">
+        <v>120.504</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>mc_014</t>
+          <t>mc_012</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2638,31 +2924,34 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-0.0274</v>
+        <v>0.1573</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0414</v>
+        <v>0.0517</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0415</v>
+        <v>0.1421</v>
       </c>
       <c r="F23" t="n">
-        <v>46073.6367</v>
+        <v>-0.0109</v>
       </c>
       <c r="G23" t="n">
-        <v>4.601</v>
+        <v>47798.4023</v>
       </c>
       <c r="H23" t="n">
-        <v>62.5754</v>
+        <v>4.4604</v>
       </c>
       <c r="I23" t="n">
-        <v>125.0859</v>
+        <v>67.122</v>
+      </c>
+      <c r="J23" t="n">
+        <v>116.6349</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>mc_015</t>
+          <t>mc_013</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2671,31 +2960,34 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-0.1445</v>
+        <v>0.1731</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1922</v>
+        <v>-0.1708</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0038</v>
+        <v>-0.0372</v>
       </c>
       <c r="F24" t="n">
-        <v>48435.5742</v>
+        <v>0.0924</v>
       </c>
       <c r="G24" t="n">
-        <v>5.0573</v>
+        <v>54160.7188</v>
       </c>
       <c r="H24" t="n">
-        <v>67.9319</v>
+        <v>5.073</v>
       </c>
       <c r="I24" t="n">
-        <v>123.9796</v>
+        <v>78.038</v>
+      </c>
+      <c r="J24" t="n">
+        <v>119.6822</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>mc_016</t>
+          <t>mc_014</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2704,31 +2996,34 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-0.0145</v>
+        <v>-0.0274</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0897</v>
+        <v>0.0414</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1269</v>
+        <v>0.0415</v>
       </c>
       <c r="F25" t="n">
-        <v>46856.125</v>
+        <v>0.1346</v>
       </c>
       <c r="G25" t="n">
-        <v>4.6061</v>
+        <v>53447.2969</v>
       </c>
       <c r="H25" t="n">
-        <v>63.9705</v>
+        <v>4.9371</v>
       </c>
       <c r="I25" t="n">
-        <v>127.6017</v>
+        <v>75.637</v>
+      </c>
+      <c r="J25" t="n">
+        <v>118.3982</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>mc_017</t>
+          <t>mc_015</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2737,31 +3032,34 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.0252</v>
+        <v>-0.1445</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.0352</v>
+        <v>-0.1922</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0317</v>
+        <v>0.0038</v>
       </c>
       <c r="F26" t="n">
-        <v>49000.3047</v>
+        <v>-0.1333</v>
       </c>
       <c r="G26" t="n">
-        <v>4.6748</v>
+        <v>42399.5742</v>
       </c>
       <c r="H26" t="n">
-        <v>69.3158</v>
+        <v>4.4787</v>
       </c>
       <c r="I26" t="n">
-        <v>121.1682</v>
+        <v>56.5007</v>
+      </c>
+      <c r="J26" t="n">
+        <v>127.7985</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>mc_018</t>
+          <t>mc_016</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2770,31 +3068,34 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.1531</v>
+        <v>-0.0145</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.0575</v>
+        <v>0.0897</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.1404</v>
+        <v>0.1269</v>
       </c>
       <c r="F27" t="n">
-        <v>48564.7383</v>
+        <v>0.0098</v>
       </c>
       <c r="G27" t="n">
-        <v>4.7471</v>
+        <v>47120.6797</v>
       </c>
       <c r="H27" t="n">
-        <v>67.95180000000001</v>
+        <v>4.6085</v>
       </c>
       <c r="I27" t="n">
-        <v>118.0202</v>
+        <v>64.2597</v>
+      </c>
+      <c r="J27" t="n">
+        <v>126.3245</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>mc_019</t>
+          <t>mc_017</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2803,31 +3104,34 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.1208</v>
+        <v>0.0252</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0083</v>
+        <v>-0.0352</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.118</v>
+        <v>0.0317</v>
       </c>
       <c r="F28" t="n">
-        <v>48886.2031</v>
+        <v>0.0349</v>
       </c>
       <c r="G28" t="n">
-        <v>4.6367</v>
+        <v>51002.7969</v>
       </c>
       <c r="H28" t="n">
-        <v>69.37949999999999</v>
+        <v>4.8214</v>
       </c>
       <c r="I28" t="n">
-        <v>116.7749</v>
+        <v>72.5149</v>
+      </c>
+      <c r="J28" t="n">
+        <v>119.4421</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>mc_020</t>
+          <t>mc_018</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2836,31 +3140,34 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.1053</v>
+        <v>0.1531</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.0396</v>
+        <v>-0.0575</v>
       </c>
       <c r="E29" t="n">
-        <v>0.08649999999999999</v>
+        <v>-0.1404</v>
       </c>
       <c r="F29" t="n">
-        <v>48592.7656</v>
+        <v>0.0677</v>
       </c>
       <c r="G29" t="n">
-        <v>4.5645</v>
+        <v>53330.1484</v>
       </c>
       <c r="H29" t="n">
-        <v>67.72490000000001</v>
+        <v>5.404</v>
       </c>
       <c r="I29" t="n">
-        <v>120.4156</v>
+        <v>75.48869999999999</v>
+      </c>
+      <c r="J29" t="n">
+        <v>120.2279</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>mc_021</t>
+          <t>mc_019</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2869,31 +3176,34 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-0.094</v>
+        <v>0.1208</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1771</v>
+        <v>0.0083</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1484</v>
+        <v>-0.118</v>
       </c>
       <c r="F30" t="n">
-        <v>46950.8008</v>
+        <v>-0.1358</v>
       </c>
       <c r="G30" t="n">
-        <v>4.3501</v>
+        <v>41256.4531</v>
       </c>
       <c r="H30" t="n">
-        <v>64.0949</v>
+        <v>4.2084</v>
       </c>
       <c r="I30" t="n">
-        <v>129.4288</v>
+        <v>55.3002</v>
+      </c>
+      <c r="J30" t="n">
+        <v>124.4349</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>mc_022</t>
+          <t>mc_020</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2902,31 +3212,34 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-0.0462</v>
+        <v>0.1053</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1417</v>
+        <v>-0.0396</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0528</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="F31" t="n">
-        <v>46562.7109</v>
+        <v>0.1047</v>
       </c>
       <c r="G31" t="n">
-        <v>4.4602</v>
+        <v>55227.4375</v>
       </c>
       <c r="H31" t="n">
-        <v>63.804</v>
+        <v>5.0706</v>
       </c>
       <c r="I31" t="n">
-        <v>124.9369</v>
+        <v>80.3477</v>
+      </c>
+      <c r="J31" t="n">
+        <v>119.5203</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>mc_023</t>
+          <t>mc_021</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2935,31 +3248,34 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-0.1513</v>
+        <v>-0.094</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.07099999999999999</v>
+        <v>0.1771</v>
       </c>
       <c r="E32" t="n">
-        <v>0.0654</v>
+        <v>0.1484</v>
       </c>
       <c r="F32" t="n">
-        <v>49036.2266</v>
+        <v>-0.1581</v>
       </c>
       <c r="G32" t="n">
-        <v>4.4809</v>
+        <v>38861.1133</v>
       </c>
       <c r="H32" t="n">
-        <v>68.9367</v>
+        <v>4.0659</v>
       </c>
       <c r="I32" t="n">
-        <v>121.1177</v>
+        <v>51.0779</v>
+      </c>
+      <c r="J32" t="n">
+        <v>127.7171</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>mc_024</t>
+          <t>mc_022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2968,31 +3284,34 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.1347</v>
+        <v>-0.0462</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.0142</v>
+        <v>0.1417</v>
       </c>
       <c r="E33" t="n">
-        <v>0.1197</v>
+        <v>0.0528</v>
       </c>
       <c r="F33" t="n">
-        <v>49951.1445</v>
+        <v>-0.1383</v>
       </c>
       <c r="G33" t="n">
-        <v>4.6242</v>
+        <v>39864.2422</v>
       </c>
       <c r="H33" t="n">
-        <v>69.663</v>
+        <v>4.4068</v>
       </c>
       <c r="I33" t="n">
-        <v>117.7069</v>
+        <v>52.4454</v>
+      </c>
+      <c r="J33" t="n">
+        <v>128.9563</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>mc_025</t>
+          <t>mc_023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3001,31 +3320,34 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.1792</v>
+        <v>-0.1513</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0045</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>0.08069999999999999</v>
+        <v>0.0654</v>
       </c>
       <c r="F34" t="n">
-        <v>49145.2344</v>
+        <v>0.0613</v>
       </c>
       <c r="G34" t="n">
-        <v>4.7316</v>
+        <v>52855.9062</v>
       </c>
       <c r="H34" t="n">
-        <v>69.0034</v>
+        <v>5.0014</v>
       </c>
       <c r="I34" t="n">
-        <v>116.8202</v>
+        <v>75.1142</v>
+      </c>
+      <c r="J34" t="n">
+        <v>119.6903</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>mc_026</t>
+          <t>mc_024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3034,31 +3356,34 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.0269</v>
+        <v>0.1347</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.1066</v>
+        <v>-0.0142</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.0203</v>
+        <v>0.1197</v>
       </c>
       <c r="F35" t="n">
-        <v>48998.4766</v>
+        <v>-0.0464</v>
       </c>
       <c r="G35" t="n">
-        <v>4.5546</v>
+        <v>46749.8789</v>
       </c>
       <c r="H35" t="n">
-        <v>69.3105</v>
+        <v>4.6241</v>
       </c>
       <c r="I35" t="n">
-        <v>120.0727</v>
+        <v>64.5394</v>
+      </c>
+      <c r="J35" t="n">
+        <v>120.2884</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>mc_027</t>
+          <t>mc_025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3067,31 +3392,34 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.002</v>
+        <v>0.1792</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.1516</v>
+        <v>0.0045</v>
       </c>
       <c r="E36" t="n">
-        <v>0.1158</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="F36" t="n">
-        <v>46690.6953</v>
+        <v>0.1133</v>
       </c>
       <c r="G36" t="n">
-        <v>4.5828</v>
+        <v>54435.1562</v>
       </c>
       <c r="H36" t="n">
-        <v>64.7033</v>
+        <v>5.2829</v>
       </c>
       <c r="I36" t="n">
-        <v>122.0837</v>
+        <v>78.6383</v>
+      </c>
+      <c r="J36" t="n">
+        <v>118.023</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>mc_028</t>
+          <t>mc_026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3100,31 +3428,34 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.0429</v>
+        <v>0.0269</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0306</v>
+        <v>-0.1066</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.1224</v>
+        <v>-0.0203</v>
       </c>
       <c r="F37" t="n">
-        <v>49234.3047</v>
+        <v>0.1667</v>
       </c>
       <c r="G37" t="n">
-        <v>4.7648</v>
+        <v>56937.832</v>
       </c>
       <c r="H37" t="n">
-        <v>69.90779999999999</v>
+        <v>5.3629</v>
       </c>
       <c r="I37" t="n">
-        <v>119.2592</v>
+        <v>83.2403</v>
+      </c>
+      <c r="J37" t="n">
+        <v>115.3325</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>mc_029</t>
+          <t>mc_027</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3133,31 +3464,34 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.1621</v>
+        <v>0.002</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.0223</v>
+        <v>-0.1516</v>
       </c>
       <c r="E38" t="n">
-        <v>0.0257</v>
+        <v>0.1158</v>
       </c>
       <c r="F38" t="n">
-        <v>48291.2461</v>
+        <v>0.0297</v>
       </c>
       <c r="G38" t="n">
-        <v>4.6323</v>
+        <v>48286.0039</v>
       </c>
       <c r="H38" t="n">
-        <v>67.9442</v>
+        <v>5.5182</v>
       </c>
       <c r="I38" t="n">
-        <v>117.1258</v>
+        <v>65.31699999999999</v>
+      </c>
+      <c r="J38" t="n">
+        <v>125.4875</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>mc_030</t>
+          <t>mc_028</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3166,31 +3500,34 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.1011</v>
+        <v>0.0429</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.1381</v>
+        <v>0.0306</v>
       </c>
       <c r="E39" t="n">
-        <v>0.0185</v>
+        <v>-0.1224</v>
       </c>
       <c r="F39" t="n">
-        <v>48992.3516</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="G39" t="n">
-        <v>4.678</v>
+        <v>52813.668</v>
       </c>
       <c r="H39" t="n">
-        <v>68.5898</v>
+        <v>5.1445</v>
       </c>
       <c r="I39" t="n">
-        <v>116.5734</v>
+        <v>76.7135</v>
+      </c>
+      <c r="J39" t="n">
+        <v>118.0021</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>mc_031</t>
+          <t>mc_029</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3199,31 +3536,34 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.0522</v>
+        <v>0.1621</v>
       </c>
       <c r="D40" t="n">
-        <v>0.1646</v>
+        <v>-0.0223</v>
       </c>
       <c r="E40" t="n">
-        <v>0.1228</v>
+        <v>0.0257</v>
       </c>
       <c r="F40" t="n">
-        <v>47293.543</v>
+        <v>-0.0983</v>
       </c>
       <c r="G40" t="n">
-        <v>4.5849</v>
+        <v>43137.0039</v>
       </c>
       <c r="H40" t="n">
-        <v>65.07429999999999</v>
+        <v>4.3823</v>
       </c>
       <c r="I40" t="n">
-        <v>119.5527</v>
+        <v>58.1601</v>
+      </c>
+      <c r="J40" t="n">
+        <v>123.6386</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>mc_032</t>
+          <t>mc_030</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3232,31 +3572,34 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-0.1889</v>
+        <v>0.1011</v>
       </c>
       <c r="D41" t="n">
-        <v>0.1215</v>
+        <v>-0.1381</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.1489</v>
+        <v>0.0185</v>
       </c>
       <c r="F41" t="n">
-        <v>49445.0938</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="G41" t="n">
-        <v>4.3492</v>
+        <v>43735.9219</v>
       </c>
       <c r="H41" t="n">
-        <v>70.333</v>
+        <v>4.3655</v>
       </c>
       <c r="I41" t="n">
-        <v>117.2935</v>
+        <v>57.999</v>
+      </c>
+      <c r="J41" t="n">
+        <v>127.0178</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>mc_033</t>
+          <t>mc_031</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3265,31 +3608,34 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.1922</v>
+        <v>0.0522</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0435</v>
+        <v>0.1646</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.0605</v>
+        <v>0.1228</v>
       </c>
       <c r="F42" t="n">
-        <v>48682.2148</v>
+        <v>0.0389</v>
       </c>
       <c r="G42" t="n">
-        <v>4.5817</v>
+        <v>48989.5352</v>
       </c>
       <c r="H42" t="n">
-        <v>67.9533</v>
+        <v>4.5167</v>
       </c>
       <c r="I42" t="n">
-        <v>118.6097</v>
+        <v>68.5093</v>
+      </c>
+      <c r="J42" t="n">
+        <v>119.6635</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>mc_034</t>
+          <t>mc_032</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3298,23 +3644,34 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.0304</v>
+        <v>-0.1889</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.1161</v>
+        <v>0.1215</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.029</v>
-      </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
+        <v>-0.1489</v>
+      </c>
+      <c r="F43" t="n">
+        <v>-0.0043</v>
+      </c>
+      <c r="G43" t="n">
+        <v>50619.8242</v>
+      </c>
+      <c r="H43" t="n">
+        <v>4.4924</v>
+      </c>
+      <c r="I43" t="n">
+        <v>72.8616</v>
+      </c>
+      <c r="J43" t="n">
+        <v>116.8386</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>mc_035</t>
+          <t>mc_033</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3323,23 +3680,34 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.06759999999999999</v>
+        <v>0.1922</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.0039</v>
+        <v>0.0435</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.0638</v>
-      </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
+        <v>-0.0605</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.157</v>
+      </c>
+      <c r="G44" t="n">
+        <v>58114.7305</v>
+      </c>
+      <c r="H44" t="n">
+        <v>4.9385</v>
+      </c>
+      <c r="I44" t="n">
+        <v>84.6039</v>
+      </c>
+      <c r="J44" t="n">
+        <v>117.9947</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>mc_036</t>
+          <t>mc_034</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3348,23 +3716,34 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-0.1499</v>
+        <v>0.0304</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.125</v>
+        <v>-0.1161</v>
       </c>
       <c r="E45" t="n">
-        <v>0.1475</v>
-      </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
+        <v>-0.029</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.0462</v>
+      </c>
+      <c r="G45" t="n">
+        <v>52356.332</v>
+      </c>
+      <c r="H45" t="n">
+        <v>5.4618</v>
+      </c>
+      <c r="I45" t="n">
+        <v>74.9058</v>
+      </c>
+      <c r="J45" t="n">
+        <v>116.9294</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>mc_037</t>
+          <t>mc_035</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3373,23 +3752,34 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-0.1931</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="D46" t="n">
-        <v>0.0696</v>
+        <v>-0.0039</v>
       </c>
       <c r="E46" t="n">
-        <v>0.113</v>
-      </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
+        <v>-0.0638</v>
+      </c>
+      <c r="F46" t="n">
+        <v>-0.1145</v>
+      </c>
+      <c r="G46" t="n">
+        <v>42062.3164</v>
+      </c>
+      <c r="H46" t="n">
+        <v>4.226</v>
+      </c>
+      <c r="I46" t="n">
+        <v>55.4893</v>
+      </c>
+      <c r="J46" t="n">
+        <v>128.2892</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>mc_038</t>
+          <t>mc_036</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3398,23 +3788,34 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-0.0815</v>
+        <v>-0.1499</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.09710000000000001</v>
+        <v>-0.125</v>
       </c>
       <c r="E47" t="n">
-        <v>0.1364</v>
-      </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
+        <v>0.1475</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.1431</v>
+      </c>
+      <c r="G47" t="n">
+        <v>57951.4727</v>
+      </c>
+      <c r="H47" t="n">
+        <v>4.9988</v>
+      </c>
+      <c r="I47" t="n">
+        <v>85.0724</v>
+      </c>
+      <c r="J47" t="n">
+        <v>118.893</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>mc_039</t>
+          <t>mc_037</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3423,23 +3824,34 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>-0.0426</v>
+        <v>-0.1931</v>
       </c>
       <c r="D48" t="n">
-        <v>0.1973</v>
+        <v>0.0696</v>
       </c>
       <c r="E48" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
+        <v>0.113</v>
+      </c>
+      <c r="F48" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="G48" t="n">
+        <v>40648.5391</v>
+      </c>
+      <c r="H48" t="n">
+        <v>4.3065</v>
+      </c>
+      <c r="I48" t="n">
+        <v>53.9692</v>
+      </c>
+      <c r="J48" t="n">
+        <v>129.5811</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>mc_040</t>
+          <t>mc_038</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3448,23 +3860,34 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.0851</v>
+        <v>-0.0815</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.182</v>
+        <v>-0.09710000000000001</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.1338</v>
-      </c>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
+        <v>0.1364</v>
+      </c>
+      <c r="F49" t="n">
+        <v>-0.1942</v>
+      </c>
+      <c r="G49" t="n">
+        <v>37658.207</v>
+      </c>
+      <c r="H49" t="n">
+        <v>4.1032</v>
+      </c>
+      <c r="I49" t="n">
+        <v>47.8113</v>
+      </c>
+      <c r="J49" t="n">
+        <v>132.4297</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>mc_041</t>
+          <t>mc_039</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3473,23 +3896,34 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-0.1678</v>
+        <v>-0.0426</v>
       </c>
       <c r="D50" t="n">
-        <v>0.1884</v>
+        <v>0.1973</v>
       </c>
       <c r="E50" t="n">
-        <v>0.0015</v>
-      </c>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
+        <v>0.03</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.1527</v>
+      </c>
+      <c r="G50" t="n">
+        <v>53659.3203</v>
+      </c>
+      <c r="H50" t="n">
+        <v>4.9615</v>
+      </c>
+      <c r="I50" t="n">
+        <v>75.5401</v>
+      </c>
+      <c r="J50" t="n">
+        <v>125.4192</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>mc_042</t>
+          <t>mc_040</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3498,23 +3932,34 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-0.1237</v>
+        <v>0.0851</v>
       </c>
       <c r="D51" t="n">
-        <v>0.1437</v>
+        <v>-0.182</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.0761</v>
-      </c>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
+        <v>-0.1338</v>
+      </c>
+      <c r="F51" t="n">
+        <v>-0.0468</v>
+      </c>
+      <c r="G51" t="n">
+        <v>46309.3555</v>
+      </c>
+      <c r="H51" t="n">
+        <v>4.7369</v>
+      </c>
+      <c r="I51" t="n">
+        <v>63.6127</v>
+      </c>
+      <c r="J51" t="n">
+        <v>120.7411</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>mc_043</t>
+          <t>mc_041</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3523,23 +3968,34 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.1279</v>
+        <v>-0.1678</v>
       </c>
       <c r="D52" t="n">
-        <v>0.0936</v>
+        <v>0.1884</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.0697</v>
-      </c>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
+        <v>0.0015</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.0891</v>
+      </c>
+      <c r="G52" t="n">
+        <v>54072.457</v>
+      </c>
+      <c r="H52" t="n">
+        <v>4.5583</v>
+      </c>
+      <c r="I52" t="n">
+        <v>79.1495</v>
+      </c>
+      <c r="J52" t="n">
+        <v>116.9947</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>mc_044</t>
+          <t>mc_042</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3548,23 +4004,34 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-0.1723</v>
+        <v>-0.1237</v>
       </c>
       <c r="D53" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.1437</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.1432</v>
-      </c>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
+        <v>-0.0761</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="G53" t="n">
+        <v>48295.4062</v>
+      </c>
+      <c r="H53" t="n">
+        <v>4.8018</v>
+      </c>
+      <c r="I53" t="n">
+        <v>66.7598</v>
+      </c>
+      <c r="J53" t="n">
+        <v>126.2479</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>mc_045</t>
+          <t>mc_043</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3573,23 +4040,34 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-0.0256</v>
+        <v>0.1279</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.1306</v>
+        <v>0.0936</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.0452</v>
-      </c>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
+        <v>-0.0697</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.1184</v>
+      </c>
+      <c r="G54" t="n">
+        <v>55700.6289</v>
+      </c>
+      <c r="H54" t="n">
+        <v>4.7827</v>
+      </c>
+      <c r="I54" t="n">
+        <v>81.4526</v>
+      </c>
+      <c r="J54" t="n">
+        <v>120.8769</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>mc_046</t>
+          <t>mc_044</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3598,23 +4076,34 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0.0471</v>
+        <v>-0.1723</v>
       </c>
       <c r="D55" t="n">
-        <v>0.0213</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="E55" t="n">
-        <v>0.1023</v>
-      </c>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
+        <v>-0.1432</v>
+      </c>
+      <c r="F55" t="n">
+        <v>-0.0649</v>
+      </c>
+      <c r="G55" t="n">
+        <v>44701.5</v>
+      </c>
+      <c r="H55" t="n">
+        <v>4.4354</v>
+      </c>
+      <c r="I55" t="n">
+        <v>60.1034</v>
+      </c>
+      <c r="J55" t="n">
+        <v>129.6498</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>mc_047</t>
+          <t>mc_045</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3623,23 +4112,34 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>0.0555</v>
+        <v>-0.0256</v>
       </c>
       <c r="D56" t="n">
-        <v>0.1024</v>
+        <v>-0.1306</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.1385</v>
-      </c>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
+        <v>-0.0452</v>
+      </c>
+      <c r="F56" t="n">
+        <v>-0.1112</v>
+      </c>
+      <c r="G56" t="n">
+        <v>41322.1016</v>
+      </c>
+      <c r="H56" t="n">
+        <v>4.748</v>
+      </c>
+      <c r="I56" t="n">
+        <v>54.0596</v>
+      </c>
+      <c r="J56" t="n">
+        <v>128.5773</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>mc_048</t>
+          <t>mc_046</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3648,23 +4148,34 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0.1127</v>
+        <v>0.0471</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.0283</v>
+        <v>0.0213</v>
       </c>
       <c r="E57" t="n">
-        <v>0.0984</v>
-      </c>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
+        <v>0.1023</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.1854</v>
+      </c>
+      <c r="G57" t="n">
+        <v>59354.9922</v>
+      </c>
+      <c r="H57" t="n">
+        <v>5.2469</v>
+      </c>
+      <c r="I57" t="n">
+        <v>88.02679999999999</v>
+      </c>
+      <c r="J57" t="n">
+        <v>116.2165</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>mc_049</t>
+          <t>mc_047</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3673,23 +4184,34 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>-0.0051</v>
+        <v>0.0555</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.06419999999999999</v>
+        <v>0.1024</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.09080000000000001</v>
-      </c>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
+        <v>-0.1385</v>
+      </c>
+      <c r="F58" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="G58" t="n">
+        <v>42418.8516</v>
+      </c>
+      <c r="H58" t="n">
+        <v>4.5328</v>
+      </c>
+      <c r="I58" t="n">
+        <v>56.8029</v>
+      </c>
+      <c r="J58" t="n">
+        <v>126.2573</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>mc_050</t>
+          <t>mc_048</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3698,23 +4220,34 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.1127</v>
       </c>
       <c r="D59" t="n">
-        <v>0.0577</v>
+        <v>-0.0283</v>
       </c>
       <c r="E59" t="n">
-        <v>0.1324</v>
-      </c>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
+        <v>0.0984</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.0238</v>
+      </c>
+      <c r="G59" t="n">
+        <v>49641.4688</v>
+      </c>
+      <c r="H59" t="n">
+        <v>4.5755</v>
+      </c>
+      <c r="I59" t="n">
+        <v>69.48739999999999</v>
+      </c>
+      <c r="J59" t="n">
+        <v>117.6498</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>mc_051</t>
+          <t>mc_049</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3723,23 +4256,34 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>-0.1368</v>
+        <v>-0.0051</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.0118</v>
+        <v>-0.06419999999999999</v>
       </c>
       <c r="E60" t="n">
-        <v>0.0699</v>
-      </c>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
+        <v>-0.09080000000000001</v>
+      </c>
+      <c r="F60" t="n">
+        <v>-0.07530000000000001</v>
+      </c>
+      <c r="G60" t="n">
+        <v>43213.1289</v>
+      </c>
+      <c r="H60" t="n">
+        <v>4.5328</v>
+      </c>
+      <c r="I60" t="n">
+        <v>57.5283</v>
+      </c>
+      <c r="J60" t="n">
+        <v>126.7507</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>mc_052</t>
+          <t>mc_050</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3748,23 +4292,34 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>0.09229999999999999</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.1104</v>
+        <v>0.0577</v>
       </c>
       <c r="E61" t="n">
-        <v>0.0382</v>
-      </c>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
+        <v>0.1324</v>
+      </c>
+      <c r="F61" t="n">
+        <v>-0.199</v>
+      </c>
+      <c r="G61" t="n">
+        <v>38129.3711</v>
+      </c>
+      <c r="H61" t="n">
+        <v>4.1345</v>
+      </c>
+      <c r="I61" t="n">
+        <v>49.1287</v>
+      </c>
+      <c r="J61" t="n">
+        <v>126.1903</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>mc_053</t>
+          <t>mc_051</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3773,23 +4328,34 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>0.07580000000000001</v>
+        <v>-0.1368</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.0073</v>
+        <v>-0.0118</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.1302</v>
-      </c>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
+        <v>0.0699</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.1556</v>
+      </c>
+      <c r="G62" t="n">
+        <v>57048.4531</v>
+      </c>
+      <c r="H62" t="n">
+        <v>5.0595</v>
+      </c>
+      <c r="I62" t="n">
+        <v>83.1465</v>
+      </c>
+      <c r="J62" t="n">
+        <v>115.9316</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>mc_054</t>
+          <t>mc_052</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3798,23 +4364,34 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>-0.1804</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.0756</v>
+        <v>-0.1104</v>
       </c>
       <c r="E63" t="n">
-        <v>0.1043</v>
-      </c>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
+        <v>0.0382</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G63" t="n">
+        <v>54163.5078</v>
+      </c>
+      <c r="H63" t="n">
+        <v>5.5597</v>
+      </c>
+      <c r="I63" t="n">
+        <v>78.6165</v>
+      </c>
+      <c r="J63" t="n">
+        <v>118.6421</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>mc_055</t>
+          <t>mc_053</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3823,23 +4400,34 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>-0.0693</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="D64" t="n">
-        <v>0.0196</v>
+        <v>-0.0073</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.0303</v>
-      </c>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
+        <v>-0.1302</v>
+      </c>
+      <c r="F64" t="n">
+        <v>-0.1058</v>
+      </c>
+      <c r="G64" t="n">
+        <v>43551.1875</v>
+      </c>
+      <c r="H64" t="n">
+        <v>4.284</v>
+      </c>
+      <c r="I64" t="n">
+        <v>58.634</v>
+      </c>
+      <c r="J64" t="n">
+        <v>122.6298</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>mc_056</t>
+          <t>mc_054</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3848,23 +4436,34 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>-0.0512</v>
+        <v>-0.1804</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.1087</v>
+        <v>-0.0756</v>
       </c>
       <c r="E65" t="n">
-        <v>0.08790000000000001</v>
-      </c>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
+        <v>0.1043</v>
+      </c>
+      <c r="F65" t="n">
+        <v>-0.154</v>
+      </c>
+      <c r="G65" t="n">
+        <v>41948</v>
+      </c>
+      <c r="H65" t="n">
+        <v>4.3849</v>
+      </c>
+      <c r="I65" t="n">
+        <v>56.457</v>
+      </c>
+      <c r="J65" t="n">
+        <v>127.4444</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>mc_057</t>
+          <t>mc_055</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3873,23 +4472,34 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>-0.09089999999999999</v>
+        <v>-0.0693</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.1777</v>
+        <v>0.0196</v>
       </c>
       <c r="E66" t="n">
-        <v>0.0524</v>
-      </c>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
+        <v>-0.0303</v>
+      </c>
+      <c r="F66" t="n">
+        <v>-0.0721</v>
+      </c>
+      <c r="G66" t="n">
+        <v>43705.6523</v>
+      </c>
+      <c r="H66" t="n">
+        <v>4.266</v>
+      </c>
+      <c r="I66" t="n">
+        <v>58.4881</v>
+      </c>
+      <c r="J66" t="n">
+        <v>129.3185</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>mc_058</t>
+          <t>mc_056</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3898,23 +4508,34 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>-0.0539</v>
+        <v>-0.0512</v>
       </c>
       <c r="D67" t="n">
-        <v>0.0824</v>
+        <v>-0.1087</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.0106</v>
-      </c>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
+        <v>0.08790000000000001</v>
+      </c>
+      <c r="F67" t="n">
+        <v>-0.0776</v>
+      </c>
+      <c r="G67" t="n">
+        <v>43921.2969</v>
+      </c>
+      <c r="H67" t="n">
+        <v>4.5505</v>
+      </c>
+      <c r="I67" t="n">
+        <v>58.8175</v>
+      </c>
+      <c r="J67" t="n">
+        <v>122.7641</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>mc_059</t>
+          <t>mc_057</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3923,23 +4544,34 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>-0.0622</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="D68" t="n">
-        <v>0.1747</v>
+        <v>-0.1777</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.1071</v>
-      </c>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
+        <v>0.0524</v>
+      </c>
+      <c r="F68" t="n">
+        <v>-0.083</v>
+      </c>
+      <c r="G68" t="n">
+        <v>43360.25</v>
+      </c>
+      <c r="H68" t="n">
+        <v>4.209</v>
+      </c>
+      <c r="I68" t="n">
+        <v>58.3202</v>
+      </c>
+      <c r="J68" t="n">
+        <v>129.5991</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>mc_060</t>
+          <t>mc_058</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3948,23 +4580,34 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>0.0456</v>
+        <v>-0.0539</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.1006</v>
+        <v>0.0824</v>
       </c>
       <c r="E69" t="n">
-        <v>0.1214</v>
-      </c>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
+        <v>-0.0106</v>
+      </c>
+      <c r="F69" t="n">
+        <v>-0.1646</v>
+      </c>
+      <c r="G69" t="n">
+        <v>38927.1328</v>
+      </c>
+      <c r="H69" t="n">
+        <v>4.3371</v>
+      </c>
+      <c r="I69" t="n">
+        <v>49.1786</v>
+      </c>
+      <c r="J69" t="n">
+        <v>135.6326</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>mc_061</t>
+          <t>mc_059</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3973,23 +4616,34 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>0.07870000000000001</v>
+        <v>-0.0622</v>
       </c>
       <c r="D70" t="n">
-        <v>0.0482</v>
+        <v>0.1747</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.07969999999999999</v>
-      </c>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
+        <v>-0.1071</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0.0951</v>
+      </c>
+      <c r="G70" t="n">
+        <v>52594.2344</v>
+      </c>
+      <c r="H70" t="n">
+        <v>5.0828</v>
+      </c>
+      <c r="I70" t="n">
+        <v>73.1215</v>
+      </c>
+      <c r="J70" t="n">
+        <v>123.0913</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>mc_062</t>
+          <t>mc_060</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3998,23 +4652,34 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>-0.07199999999999999</v>
+        <v>0.0456</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.1168</v>
+        <v>-0.1006</v>
       </c>
       <c r="E71" t="n">
-        <v>0.0343</v>
-      </c>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
+        <v>0.1214</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0.0594</v>
+      </c>
+      <c r="G71" t="n">
+        <v>53030.6875</v>
+      </c>
+      <c r="H71" t="n">
+        <v>5.1183</v>
+      </c>
+      <c r="I71" t="n">
+        <v>76.03270000000001</v>
+      </c>
+      <c r="J71" t="n">
+        <v>117.8757</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>mc_063</t>
+          <t>mc_061</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4023,23 +4688,34 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>-0.0997</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.0169</v>
+        <v>0.0482</v>
       </c>
       <c r="E72" t="n">
-        <v>0.0565</v>
-      </c>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
+        <v>-0.07969999999999999</v>
+      </c>
+      <c r="F72" t="n">
+        <v>-0.1929</v>
+      </c>
+      <c r="G72" t="n">
+        <v>38383.4648</v>
+      </c>
+      <c r="H72" t="n">
+        <v>4.1433</v>
+      </c>
+      <c r="I72" t="n">
+        <v>49.4097</v>
+      </c>
+      <c r="J72" t="n">
+        <v>128.7111</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>mc_064</t>
+          <t>mc_062</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4048,23 +4724,34 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>-0.0755</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="D73" t="n">
-        <v>0.183</v>
+        <v>-0.1168</v>
       </c>
       <c r="E73" t="n">
-        <v>-0.0886</v>
-      </c>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
+        <v>0.0343</v>
+      </c>
+      <c r="F73" t="n">
+        <v>-0.0683</v>
+      </c>
+      <c r="G73" t="n">
+        <v>43426.8867</v>
+      </c>
+      <c r="H73" t="n">
+        <v>4.4766</v>
+      </c>
+      <c r="I73" t="n">
+        <v>57.2184</v>
+      </c>
+      <c r="J73" t="n">
+        <v>130.7307</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>mc_065</t>
+          <t>mc_063</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4073,23 +4760,34 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>0.0599</v>
+        <v>-0.0997</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.0303</v>
+        <v>-0.0169</v>
       </c>
       <c r="E74" t="n">
-        <v>-0.0504</v>
-      </c>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
+        <v>0.0565</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.1762</v>
+      </c>
+      <c r="G74" t="n">
+        <v>57967.3828</v>
+      </c>
+      <c r="H74" t="n">
+        <v>5.386</v>
+      </c>
+      <c r="I74" t="n">
+        <v>83.09910000000001</v>
+      </c>
+      <c r="J74" t="n">
+        <v>115.9162</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>mc_066</t>
+          <t>mc_064</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4098,23 +4796,34 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>0.0141</v>
+        <v>-0.0755</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.0495</v>
+        <v>0.183</v>
       </c>
       <c r="E75" t="n">
-        <v>0.0219</v>
-      </c>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
+        <v>-0.0886</v>
+      </c>
+      <c r="F75" t="n">
+        <v>-0.091</v>
+      </c>
+      <c r="G75" t="n">
+        <v>42248.4844</v>
+      </c>
+      <c r="H75" t="n">
+        <v>4.2319</v>
+      </c>
+      <c r="I75" t="n">
+        <v>55.4785</v>
+      </c>
+      <c r="J75" t="n">
+        <v>131.4638</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>mc_067</t>
+          <t>mc_065</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4123,23 +4832,34 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>-0.1763</v>
+        <v>0.0599</v>
       </c>
       <c r="D76" t="n">
-        <v>0.0722</v>
+        <v>-0.0303</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.0398</v>
-      </c>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
+        <v>-0.0504</v>
+      </c>
+      <c r="F76" t="n">
+        <v>-0.0428</v>
+      </c>
+      <c r="G76" t="n">
+        <v>46744.5</v>
+      </c>
+      <c r="H76" t="n">
+        <v>4.426</v>
+      </c>
+      <c r="I76" t="n">
+        <v>65.6819</v>
+      </c>
+      <c r="J76" t="n">
+        <v>123.9673</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>mc_068</t>
+          <t>mc_066</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4148,23 +4868,34 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>0.0712</v>
+        <v>0.0141</v>
       </c>
       <c r="D77" t="n">
-        <v>-0.0009</v>
+        <v>-0.0495</v>
       </c>
       <c r="E77" t="n">
-        <v>-0.0081</v>
-      </c>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
+        <v>0.0219</v>
+      </c>
+      <c r="F77" t="n">
+        <v>-0.1205</v>
+      </c>
+      <c r="G77" t="n">
+        <v>41301.2188</v>
+      </c>
+      <c r="H77" t="n">
+        <v>4.3438</v>
+      </c>
+      <c r="I77" t="n">
+        <v>54.3827</v>
+      </c>
+      <c r="J77" t="n">
+        <v>126.5116</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>mc_069</t>
+          <t>mc_067</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4173,23 +4904,34 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>-0.0097</v>
+        <v>-0.1763</v>
       </c>
       <c r="D78" t="n">
-        <v>0.1851</v>
+        <v>0.0722</v>
       </c>
       <c r="E78" t="n">
-        <v>-0.1161</v>
-      </c>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
+        <v>-0.0398</v>
+      </c>
+      <c r="F78" t="n">
+        <v>-0.1826</v>
+      </c>
+      <c r="G78" t="n">
+        <v>38851.6094</v>
+      </c>
+      <c r="H78" t="n">
+        <v>4.0214</v>
+      </c>
+      <c r="I78" t="n">
+        <v>50.8853</v>
+      </c>
+      <c r="J78" t="n">
+        <v>127.5389</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>mc_070</t>
+          <t>mc_068</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4198,23 +4940,34 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>-0.1058</v>
+        <v>0.0712</v>
       </c>
       <c r="D79" t="n">
-        <v>-0.1416</v>
+        <v>-0.0009</v>
       </c>
       <c r="E79" t="n">
-        <v>-0.0945</v>
-      </c>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
+        <v>-0.0081</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0.08359999999999999</v>
+      </c>
+      <c r="G79" t="n">
+        <v>51131.0898</v>
+      </c>
+      <c r="H79" t="n">
+        <v>5.0455</v>
+      </c>
+      <c r="I79" t="n">
+        <v>71.1033</v>
+      </c>
+      <c r="J79" t="n">
+        <v>121.2948</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>mc_071</t>
+          <t>mc_069</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4223,23 +4976,34 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>0.1497</v>
+        <v>-0.0097</v>
       </c>
       <c r="D80" t="n">
-        <v>0.0107</v>
+        <v>0.1851</v>
       </c>
       <c r="E80" t="n">
-        <v>0.0159</v>
-      </c>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
+        <v>-0.1161</v>
+      </c>
+      <c r="F80" t="n">
+        <v>-0.1031</v>
+      </c>
+      <c r="G80" t="n">
+        <v>41946.1523</v>
+      </c>
+      <c r="H80" t="n">
+        <v>4.5027</v>
+      </c>
+      <c r="I80" t="n">
+        <v>55.3756</v>
+      </c>
+      <c r="J80" t="n">
+        <v>127.7849</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>mc_072</t>
+          <t>mc_070</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4248,23 +5012,34 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>-0.1789</v>
+        <v>-0.1058</v>
       </c>
       <c r="D81" t="n">
-        <v>-0.1628</v>
+        <v>-0.1416</v>
       </c>
       <c r="E81" t="n">
-        <v>0.0113</v>
-      </c>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
+        <v>-0.0945</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0.1893</v>
+      </c>
+      <c r="G81" t="n">
+        <v>59404.7344</v>
+      </c>
+      <c r="H81" t="n">
+        <v>5.4319</v>
+      </c>
+      <c r="I81" t="n">
+        <v>85.78</v>
+      </c>
+      <c r="J81" t="n">
+        <v>116.464</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>mc_073</t>
+          <t>mc_071</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4273,23 +5048,34 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>0.1153</v>
+        <v>0.1497</v>
       </c>
       <c r="D82" t="n">
-        <v>0.1093</v>
+        <v>0.0107</v>
       </c>
       <c r="E82" t="n">
-        <v>-0.0229</v>
-      </c>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
+        <v>0.0159</v>
+      </c>
+      <c r="F82" t="n">
+        <v>-0.1839</v>
+      </c>
+      <c r="G82" t="n">
+        <v>38740.793</v>
+      </c>
+      <c r="H82" t="n">
+        <v>4.0913</v>
+      </c>
+      <c r="I82" t="n">
+        <v>50.7957</v>
+      </c>
+      <c r="J82" t="n">
+        <v>131.3434</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>mc_074</t>
+          <t>mc_072</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4298,23 +5084,34 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>0.1875</v>
+        <v>-0.1789</v>
       </c>
       <c r="D83" t="n">
-        <v>-0.0795</v>
+        <v>-0.1628</v>
       </c>
       <c r="E83" t="n">
-        <v>0.09470000000000001</v>
-      </c>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
+        <v>0.0113</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0.0163</v>
+      </c>
+      <c r="G83" t="n">
+        <v>49518.6602</v>
+      </c>
+      <c r="H83" t="n">
+        <v>4.9152</v>
+      </c>
+      <c r="I83" t="n">
+        <v>68.636</v>
+      </c>
+      <c r="J83" t="n">
+        <v>122.8966</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>mc_075</t>
+          <t>mc_073</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4323,23 +5120,34 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>0.0056</v>
+        <v>0.1153</v>
       </c>
       <c r="D84" t="n">
-        <v>-0.0842</v>
+        <v>0.1093</v>
       </c>
       <c r="E84" t="n">
-        <v>0.1053</v>
-      </c>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
+        <v>-0.0229</v>
+      </c>
+      <c r="F84" t="n">
+        <v>-0.0208</v>
+      </c>
+      <c r="G84" t="n">
+        <v>47084.4727</v>
+      </c>
+      <c r="H84" t="n">
+        <v>4.5088</v>
+      </c>
+      <c r="I84" t="n">
+        <v>65.8573</v>
+      </c>
+      <c r="J84" t="n">
+        <v>118.796</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>mc_076</t>
+          <t>mc_074</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4348,23 +5156,34 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>-0.0496</v>
+        <v>0.1875</v>
       </c>
       <c r="D85" t="n">
-        <v>0.0603</v>
+        <v>-0.0795</v>
       </c>
       <c r="E85" t="n">
-        <v>-0.0964</v>
-      </c>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
+        <v>0.09470000000000001</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0.1096</v>
+      </c>
+      <c r="G85" t="n">
+        <v>54849.5312</v>
+      </c>
+      <c r="H85" t="n">
+        <v>5.0543</v>
+      </c>
+      <c r="I85" t="n">
+        <v>79.44240000000001</v>
+      </c>
+      <c r="J85" t="n">
+        <v>119.1167</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>mc_077</t>
+          <t>mc_075</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4373,23 +5192,34 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>-0.0007</v>
+        <v>0.0056</v>
       </c>
       <c r="D86" t="n">
-        <v>-0.0253</v>
+        <v>-0.0842</v>
       </c>
       <c r="E86" t="n">
-        <v>0.1446</v>
-      </c>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
+        <v>0.1053</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0.1964</v>
+      </c>
+      <c r="G86" t="n">
+        <v>56914.3945</v>
+      </c>
+      <c r="H86" t="n">
+        <v>5.5569</v>
+      </c>
+      <c r="I86" t="n">
+        <v>81.5311</v>
+      </c>
+      <c r="J86" t="n">
+        <v>118.1388</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>mc_078</t>
+          <t>mc_076</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4398,23 +5228,34 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>-0.1953</v>
+        <v>-0.0496</v>
       </c>
       <c r="D87" t="n">
-        <v>-0.1299</v>
+        <v>0.0603</v>
       </c>
       <c r="E87" t="n">
-        <v>0.0915</v>
-      </c>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
+        <v>-0.0964</v>
+      </c>
+      <c r="F87" t="n">
+        <v>-0.0615</v>
+      </c>
+      <c r="G87" t="n">
+        <v>44030.6562</v>
+      </c>
+      <c r="H87" t="n">
+        <v>4.7148</v>
+      </c>
+      <c r="I87" t="n">
+        <v>58.1626</v>
+      </c>
+      <c r="J87" t="n">
+        <v>129.2291</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>mc_079</t>
+          <t>mc_077</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4423,23 +5264,34 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>0.1239</v>
+        <v>-0.0007</v>
       </c>
       <c r="D88" t="n">
-        <v>-0.0611</v>
+        <v>-0.0253</v>
       </c>
       <c r="E88" t="n">
-        <v>0.0721</v>
-      </c>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
+        <v>0.1446</v>
+      </c>
+      <c r="F88" t="n">
+        <v>-0.007900000000000001</v>
+      </c>
+      <c r="G88" t="n">
+        <v>46645.6719</v>
+      </c>
+      <c r="H88" t="n">
+        <v>4.6095</v>
+      </c>
+      <c r="I88" t="n">
+        <v>63.149</v>
+      </c>
+      <c r="J88" t="n">
+        <v>127.344</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>mc_080</t>
+          <t>mc_078</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4448,23 +5300,34 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>-0.1608</v>
+        <v>-0.1953</v>
       </c>
       <c r="D89" t="n">
-        <v>0.001</v>
+        <v>-0.1299</v>
       </c>
       <c r="E89" t="n">
-        <v>-0.0485</v>
-      </c>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
+        <v>0.0915</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0.0432</v>
+      </c>
+      <c r="G89" t="n">
+        <v>52614.3125</v>
+      </c>
+      <c r="H89" t="n">
+        <v>4.8605</v>
+      </c>
+      <c r="I89" t="n">
+        <v>75.84229999999999</v>
+      </c>
+      <c r="J89" t="n">
+        <v>117.1587</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>mc_081</t>
+          <t>mc_079</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4473,23 +5336,34 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>0.1952</v>
+        <v>0.1239</v>
       </c>
       <c r="D90" t="n">
-        <v>-0.1351</v>
+        <v>-0.0611</v>
       </c>
       <c r="E90" t="n">
-        <v>0.0956</v>
-      </c>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
+        <v>0.0721</v>
+      </c>
+      <c r="F90" t="n">
+        <v>-0.1683</v>
+      </c>
+      <c r="G90" t="n">
+        <v>39904.8203</v>
+      </c>
+      <c r="H90" t="n">
+        <v>4.5941</v>
+      </c>
+      <c r="I90" t="n">
+        <v>51.2867</v>
+      </c>
+      <c r="J90" t="n">
+        <v>127.7384</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>mc_082</t>
+          <t>mc_080</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4498,23 +5372,34 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>0.1748</v>
+        <v>-0.1608</v>
       </c>
       <c r="D91" t="n">
-        <v>-0.0424</v>
+        <v>0.001</v>
       </c>
       <c r="E91" t="n">
-        <v>0.0613</v>
-      </c>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
+        <v>-0.0485</v>
+      </c>
+      <c r="F91" t="n">
+        <v>-0.1459</v>
+      </c>
+      <c r="G91" t="n">
+        <v>41509.1875</v>
+      </c>
+      <c r="H91" t="n">
+        <v>4.2028</v>
+      </c>
+      <c r="I91" t="n">
+        <v>55.5014</v>
+      </c>
+      <c r="J91" t="n">
+        <v>130.0439</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>mc_083</t>
+          <t>mc_081</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4523,23 +5408,34 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>-0.0125</v>
+        <v>0.1952</v>
       </c>
       <c r="D92" t="n">
-        <v>0.0984</v>
+        <v>-0.1351</v>
       </c>
       <c r="E92" t="n">
-        <v>0.0788</v>
-      </c>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr"/>
+        <v>0.0956</v>
+      </c>
+      <c r="F92" t="n">
+        <v>-0.1869</v>
+      </c>
+      <c r="G92" t="n">
+        <v>38801.6562</v>
+      </c>
+      <c r="H92" t="n">
+        <v>4.1167</v>
+      </c>
+      <c r="I92" t="n">
+        <v>50.4843</v>
+      </c>
+      <c r="J92" t="n">
+        <v>128.6924</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>mc_084</t>
+          <t>mc_082</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4548,23 +5444,34 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>0.0193</v>
+        <v>0.1748</v>
       </c>
       <c r="D93" t="n">
-        <v>-0.1545</v>
+        <v>-0.0424</v>
       </c>
       <c r="E93" t="n">
-        <v>-0.1078</v>
-      </c>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr"/>
+        <v>0.0613</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0.1135</v>
+      </c>
+      <c r="G93" t="n">
+        <v>55177.543</v>
+      </c>
+      <c r="H93" t="n">
+        <v>5.845</v>
+      </c>
+      <c r="I93" t="n">
+        <v>78.9156</v>
+      </c>
+      <c r="J93" t="n">
+        <v>118.9957</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>mc_085</t>
+          <t>mc_083</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4573,23 +5480,34 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>-0.1288</v>
+        <v>-0.0125</v>
       </c>
       <c r="D94" t="n">
-        <v>0.1472</v>
+        <v>0.0984</v>
       </c>
       <c r="E94" t="n">
-        <v>-0.0341</v>
-      </c>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
+        <v>0.0788</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0.1486</v>
+      </c>
+      <c r="G94" t="n">
+        <v>53053.5586</v>
+      </c>
+      <c r="H94" t="n">
+        <v>4.8728</v>
+      </c>
+      <c r="I94" t="n">
+        <v>74.0292</v>
+      </c>
+      <c r="J94" t="n">
+        <v>125.1065</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>mc_086</t>
+          <t>mc_084</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4598,23 +5516,34 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>0.1835</v>
+        <v>0.0193</v>
       </c>
       <c r="D95" t="n">
-        <v>0.0793</v>
+        <v>-0.1545</v>
       </c>
       <c r="E95" t="n">
-        <v>-0.08690000000000001</v>
-      </c>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr"/>
+        <v>-0.1078</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0.0198</v>
+      </c>
+      <c r="G95" t="n">
+        <v>48908.8945</v>
+      </c>
+      <c r="H95" t="n">
+        <v>5.6055</v>
+      </c>
+      <c r="I95" t="n">
+        <v>67.82510000000001</v>
+      </c>
+      <c r="J95" t="n">
+        <v>120.9265</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>mc_087</t>
+          <t>mc_085</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4623,23 +5552,34 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>0.1999</v>
+        <v>-0.1288</v>
       </c>
       <c r="D96" t="n">
-        <v>0.1526</v>
+        <v>0.1472</v>
       </c>
       <c r="E96" t="n">
-        <v>0.1394</v>
-      </c>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr"/>
+        <v>-0.0341</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0.1458</v>
+      </c>
+      <c r="G96" t="n">
+        <v>57250.875</v>
+      </c>
+      <c r="H96" t="n">
+        <v>4.9642</v>
+      </c>
+      <c r="I96" t="n">
+        <v>84.50530000000001</v>
+      </c>
+      <c r="J96" t="n">
+        <v>115.6602</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>mc_088</t>
+          <t>mc_086</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4648,23 +5588,34 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>0.1401</v>
+        <v>0.1835</v>
       </c>
       <c r="D97" t="n">
-        <v>-0.1202</v>
+        <v>0.0793</v>
       </c>
       <c r="E97" t="n">
-        <v>0.0485</v>
-      </c>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
+        <v>-0.08690000000000001</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="G97" t="n">
+        <v>52853.3516</v>
+      </c>
+      <c r="H97" t="n">
+        <v>4.7019</v>
+      </c>
+      <c r="I97" t="n">
+        <v>75.80119999999999</v>
+      </c>
+      <c r="J97" t="n">
+        <v>115.9509</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>mc_089</t>
+          <t>mc_087</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4673,23 +5624,34 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>-0.0196</v>
+        <v>0.1999</v>
       </c>
       <c r="D98" t="n">
-        <v>-0.0454</v>
+        <v>0.1526</v>
       </c>
       <c r="E98" t="n">
-        <v>-0.0538</v>
-      </c>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
+        <v>0.1394</v>
+      </c>
+      <c r="F98" t="n">
+        <v>-0.025</v>
+      </c>
+      <c r="G98" t="n">
+        <v>47712.6758</v>
+      </c>
+      <c r="H98" t="n">
+        <v>4.4896</v>
+      </c>
+      <c r="I98" t="n">
+        <v>67.5061</v>
+      </c>
+      <c r="J98" t="n">
+        <v>118.0116</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>mc_090</t>
+          <t>mc_088</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4698,23 +5660,34 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>-0.1084</v>
+        <v>0.1401</v>
       </c>
       <c r="D99" t="n">
-        <v>0.1062</v>
+        <v>-0.1202</v>
       </c>
       <c r="E99" t="n">
-        <v>-0.0401</v>
-      </c>
-      <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr"/>
+        <v>0.0485</v>
+      </c>
+      <c r="F99" t="n">
+        <v>-0.0558</v>
+      </c>
+      <c r="G99" t="n">
+        <v>46142.832</v>
+      </c>
+      <c r="H99" t="n">
+        <v>4.7265</v>
+      </c>
+      <c r="I99" t="n">
+        <v>63.3574</v>
+      </c>
+      <c r="J99" t="n">
+        <v>118.5406</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>mc_091</t>
+          <t>mc_089</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4723,23 +5696,34 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>0.0207</v>
+        <v>-0.0196</v>
       </c>
       <c r="D100" t="n">
-        <v>-0.053</v>
+        <v>-0.0454</v>
       </c>
       <c r="E100" t="n">
-        <v>-0.0058</v>
-      </c>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
+        <v>-0.0538</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0.0819</v>
+      </c>
+      <c r="G100" t="n">
+        <v>51859.5781</v>
+      </c>
+      <c r="H100" t="n">
+        <v>5.0039</v>
+      </c>
+      <c r="I100" t="n">
+        <v>72.3946</v>
+      </c>
+      <c r="J100" t="n">
+        <v>117.9278</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>mc_092</t>
+          <t>mc_090</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4748,23 +5732,34 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>-0.1322</v>
+        <v>-0.1084</v>
       </c>
       <c r="D101" t="n">
-        <v>0.1333</v>
+        <v>0.1062</v>
       </c>
       <c r="E101" t="n">
-        <v>-0.1458</v>
-      </c>
-      <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr"/>
+        <v>-0.0401</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0.1025</v>
+      </c>
+      <c r="G101" t="n">
+        <v>53752.8594</v>
+      </c>
+      <c r="H101" t="n">
+        <v>4.7003</v>
+      </c>
+      <c r="I101" t="n">
+        <v>76.0107</v>
+      </c>
+      <c r="J101" t="n">
+        <v>123.757</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>mc_093</t>
+          <t>mc_091</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4773,23 +5768,34 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>-0.0781</v>
+        <v>0.0207</v>
       </c>
       <c r="D102" t="n">
-        <v>-0.176</v>
+        <v>-0.053</v>
       </c>
       <c r="E102" t="n">
-        <v>0.0073</v>
-      </c>
-      <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr"/>
+        <v>-0.0058</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0.1285</v>
+      </c>
+      <c r="G102" t="n">
+        <v>55723.9531</v>
+      </c>
+      <c r="H102" t="n">
+        <v>5.7617</v>
+      </c>
+      <c r="I102" t="n">
+        <v>79.7265</v>
+      </c>
+      <c r="J102" t="n">
+        <v>117.2887</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>mc_094</t>
+          <t>mc_092</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4798,23 +5804,34 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>-0.0201</v>
+        <v>-0.1322</v>
       </c>
       <c r="D103" t="n">
-        <v>0.08459999999999999</v>
+        <v>0.1333</v>
       </c>
       <c r="E103" t="n">
-        <v>0.0243</v>
-      </c>
-      <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr"/>
+        <v>-0.1458</v>
+      </c>
+      <c r="F103" t="n">
+        <v>-0.0174</v>
+      </c>
+      <c r="G103" t="n">
+        <v>47453.5078</v>
+      </c>
+      <c r="H103" t="n">
+        <v>4.7671</v>
+      </c>
+      <c r="I103" t="n">
+        <v>65.38800000000001</v>
+      </c>
+      <c r="J103" t="n">
+        <v>125.7098</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>mc_095</t>
+          <t>mc_093</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4823,23 +5840,34 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>0.0898</v>
+        <v>-0.0781</v>
       </c>
       <c r="D104" t="n">
-        <v>0.027</v>
+        <v>-0.176</v>
       </c>
       <c r="E104" t="n">
-        <v>0.0774</v>
-      </c>
-      <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
+        <v>0.0073</v>
+      </c>
+      <c r="F104" t="n">
+        <v>-0.0868</v>
+      </c>
+      <c r="G104" t="n">
+        <v>43360.6602</v>
+      </c>
+      <c r="H104" t="n">
+        <v>4.7441</v>
+      </c>
+      <c r="I104" t="n">
+        <v>58.0053</v>
+      </c>
+      <c r="J104" t="n">
+        <v>122.2459</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>mc_096</t>
+          <t>mc_094</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4848,23 +5876,34 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>-0.1998</v>
+        <v>-0.0201</v>
       </c>
       <c r="D105" t="n">
-        <v>-0.1472</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="E105" t="n">
-        <v>0.0741</v>
-      </c>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
+        <v>0.0243</v>
+      </c>
+      <c r="F105" t="n">
+        <v>0.0321</v>
+      </c>
+      <c r="G105" t="n">
+        <v>47620.7461</v>
+      </c>
+      <c r="H105" t="n">
+        <v>4.6197</v>
+      </c>
+      <c r="I105" t="n">
+        <v>64.688</v>
+      </c>
+      <c r="J105" t="n">
+        <v>127.5794</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>mc_097</t>
+          <t>mc_095</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4873,23 +5912,34 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>0.1328</v>
+        <v>0.0898</v>
       </c>
       <c r="D106" t="n">
-        <v>-0.185</v>
+        <v>0.027</v>
       </c>
       <c r="E106" t="n">
-        <v>0.08400000000000001</v>
-      </c>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr"/>
+        <v>0.0774</v>
+      </c>
+      <c r="F106" t="n">
+        <v>-0.09429999999999999</v>
+      </c>
+      <c r="G106" t="n">
+        <v>43229.582</v>
+      </c>
+      <c r="H106" t="n">
+        <v>4.5615</v>
+      </c>
+      <c r="I106" t="n">
+        <v>58.7796</v>
+      </c>
+      <c r="J106" t="n">
+        <v>123.4397</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>mc_098</t>
+          <t>mc_096</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4898,23 +5948,34 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>-0.1194</v>
+        <v>-0.1998</v>
       </c>
       <c r="D107" t="n">
-        <v>0.1265</v>
+        <v>-0.1472</v>
       </c>
       <c r="E107" t="n">
-        <v>0.0582</v>
-      </c>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr"/>
+        <v>0.0741</v>
+      </c>
+      <c r="F107" t="n">
+        <v>0.1328</v>
+      </c>
+      <c r="G107" t="n">
+        <v>58491.2109</v>
+      </c>
+      <c r="H107" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="I107" t="n">
+        <v>86.7551</v>
+      </c>
+      <c r="J107" t="n">
+        <v>119.4386</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>mc_099</t>
+          <t>mc_097</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4923,23 +5984,34 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>0.0827</v>
+        <v>0.1328</v>
       </c>
       <c r="D108" t="n">
-        <v>0.1671</v>
+        <v>-0.185</v>
       </c>
       <c r="E108" t="n">
-        <v>-0.0569</v>
-      </c>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr"/>
-      <c r="I108" t="inlineStr"/>
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="F108" t="n">
+        <v>-0.1748</v>
+      </c>
+      <c r="G108" t="n">
+        <v>39070.8555</v>
+      </c>
+      <c r="H108" t="n">
+        <v>4.2277</v>
+      </c>
+      <c r="I108" t="n">
+        <v>50.7066</v>
+      </c>
+      <c r="J108" t="n">
+        <v>129.0374</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>mc_100</t>
+          <t>mc_098</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4948,23 +6020,34 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>-0.0323</v>
+        <v>-0.1194</v>
       </c>
       <c r="D109" t="n">
-        <v>-0.09039999999999999</v>
+        <v>0.1265</v>
       </c>
       <c r="E109" t="n">
-        <v>-0.0737</v>
-      </c>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr"/>
+        <v>0.0582</v>
+      </c>
+      <c r="F109" t="n">
+        <v>-0.179</v>
+      </c>
+      <c r="G109" t="n">
+        <v>38463.0977</v>
+      </c>
+      <c r="H109" t="n">
+        <v>4.2913</v>
+      </c>
+      <c r="I109" t="n">
+        <v>50.0764</v>
+      </c>
+      <c r="J109" t="n">
+        <v>129.2191</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>mc_101</t>
+          <t>mc_099</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4973,23 +6056,34 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>-0.0343</v>
+        <v>0.0827</v>
       </c>
       <c r="D110" t="n">
-        <v>0.0545</v>
+        <v>0.1671</v>
       </c>
       <c r="E110" t="n">
-        <v>-0.0449</v>
-      </c>
-      <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
-      <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr"/>
+        <v>-0.0569</v>
+      </c>
+      <c r="F110" t="n">
+        <v>0.1626</v>
+      </c>
+      <c r="G110" t="n">
+        <v>56033.625</v>
+      </c>
+      <c r="H110" t="n">
+        <v>5.0979</v>
+      </c>
+      <c r="I110" t="n">
+        <v>81.7084</v>
+      </c>
+      <c r="J110" t="n">
+        <v>117.1464</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>mc_102</t>
+          <t>mc_100</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4998,23 +6092,34 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>-0.1543</v>
+        <v>-0.0323</v>
       </c>
       <c r="D111" t="n">
-        <v>-0.1992</v>
+        <v>-0.09039999999999999</v>
       </c>
       <c r="E111" t="n">
-        <v>-0.0046</v>
-      </c>
-      <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr"/>
-      <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr"/>
+        <v>-0.0737</v>
+      </c>
+      <c r="F111" t="n">
+        <v>0.0061</v>
+      </c>
+      <c r="G111" t="n">
+        <v>47610.9961</v>
+      </c>
+      <c r="H111" t="n">
+        <v>5.0081</v>
+      </c>
+      <c r="I111" t="n">
+        <v>65.0613</v>
+      </c>
+      <c r="J111" t="n">
+        <v>123.9038</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>mc_103</t>
+          <t>mc_101</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -5023,23 +6128,34 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>-0.0838</v>
+        <v>-0.0343</v>
       </c>
       <c r="D112" t="n">
-        <v>0.1622</v>
+        <v>0.0545</v>
       </c>
       <c r="E112" t="n">
-        <v>-0.0182</v>
-      </c>
-      <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
-      <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr"/>
+        <v>-0.0449</v>
+      </c>
+      <c r="F112" t="n">
+        <v>0.1999</v>
+      </c>
+      <c r="G112" t="n">
+        <v>57332.207</v>
+      </c>
+      <c r="H112" t="n">
+        <v>5.0805</v>
+      </c>
+      <c r="I112" t="n">
+        <v>82.42610000000001</v>
+      </c>
+      <c r="J112" t="n">
+        <v>115.7625</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>mc_104</t>
+          <t>mc_102</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -5048,23 +6164,34 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>0.06660000000000001</v>
+        <v>-0.1543</v>
       </c>
       <c r="D113" t="n">
-        <v>0.07340000000000001</v>
+        <v>-0.1992</v>
       </c>
       <c r="E113" t="n">
-        <v>-0.0808</v>
-      </c>
-      <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr"/>
-      <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr"/>
+        <v>-0.0046</v>
+      </c>
+      <c r="F113" t="n">
+        <v>-0.1433</v>
+      </c>
+      <c r="G113" t="n">
+        <v>41757.8164</v>
+      </c>
+      <c r="H113" t="n">
+        <v>4.2808</v>
+      </c>
+      <c r="I113" t="n">
+        <v>55.3513</v>
+      </c>
+      <c r="J113" t="n">
+        <v>128.9065</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>mc_105</t>
+          <t>mc_103</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -5073,23 +6200,34 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>0.0609</v>
+        <v>-0.0838</v>
       </c>
       <c r="D114" t="n">
-        <v>0.0384</v>
+        <v>0.1622</v>
       </c>
       <c r="E114" t="n">
-        <v>-0.0149</v>
-      </c>
-      <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr"/>
-      <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr"/>
+        <v>-0.0182</v>
+      </c>
+      <c r="F114" t="n">
+        <v>0.1817</v>
+      </c>
+      <c r="G114" t="n">
+        <v>57271.2773</v>
+      </c>
+      <c r="H114" t="n">
+        <v>5.0207</v>
+      </c>
+      <c r="I114" t="n">
+        <v>81.89279999999999</v>
+      </c>
+      <c r="J114" t="n">
+        <v>120.6243</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>mc_106</t>
+          <t>mc_104</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -5098,23 +6236,34 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>-0.1212</v>
+        <v>0.06660000000000001</v>
       </c>
       <c r="D115" t="n">
-        <v>-0.0684</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="E115" t="n">
-        <v>0.1079</v>
-      </c>
-      <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr"/>
-      <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr"/>
+        <v>-0.0808</v>
+      </c>
+      <c r="F115" t="n">
+        <v>-0.1498</v>
+      </c>
+      <c r="G115" t="n">
+        <v>40106.875</v>
+      </c>
+      <c r="H115" t="n">
+        <v>4.3491</v>
+      </c>
+      <c r="I115" t="n">
+        <v>53.017</v>
+      </c>
+      <c r="J115" t="n">
+        <v>131.1668</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>mc_107</t>
+          <t>mc_105</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -5123,23 +6272,34 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>0.1691</v>
+        <v>0.0609</v>
       </c>
       <c r="D116" t="n">
-        <v>0.1135</v>
+        <v>0.0384</v>
       </c>
       <c r="E116" t="n">
-        <v>-0.1035</v>
-      </c>
-      <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr"/>
-      <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr"/>
+        <v>-0.0149</v>
+      </c>
+      <c r="F116" t="n">
+        <v>-0.1183</v>
+      </c>
+      <c r="G116" t="n">
+        <v>42062.3516</v>
+      </c>
+      <c r="H116" t="n">
+        <v>4.2737</v>
+      </c>
+      <c r="I116" t="n">
+        <v>56.2064</v>
+      </c>
+      <c r="J116" t="n">
+        <v>125.6671</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>mc_108</t>
+          <t>mc_106</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -5148,23 +6308,34 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>0.1636</v>
+        <v>-0.1212</v>
       </c>
       <c r="D117" t="n">
-        <v>0.0914</v>
+        <v>-0.0684</v>
       </c>
       <c r="E117" t="n">
-        <v>-0.0015</v>
-      </c>
-      <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr"/>
-      <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr"/>
+        <v>0.1079</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="G117" t="n">
+        <v>52828.5352</v>
+      </c>
+      <c r="H117" t="n">
+        <v>4.9012</v>
+      </c>
+      <c r="I117" t="n">
+        <v>74.27549999999999</v>
+      </c>
+      <c r="J117" t="n">
+        <v>122.7592</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>mc_109</t>
+          <t>mc_107</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -5173,23 +6344,34 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>0.1089</v>
+        <v>0.1691</v>
       </c>
       <c r="D118" t="n">
-        <v>-0.169</v>
+        <v>0.1135</v>
       </c>
       <c r="E118" t="n">
-        <v>-0.016</v>
-      </c>
-      <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr"/>
-      <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr"/>
+        <v>-0.1035</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.1774</v>
+      </c>
+      <c r="G118" t="n">
+        <v>59515.8125</v>
+      </c>
+      <c r="H118" t="n">
+        <v>5.3296</v>
+      </c>
+      <c r="I118" t="n">
+        <v>86.9995</v>
+      </c>
+      <c r="J118" t="n">
+        <v>116.9317</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>mc_110</t>
+          <t>mc_108</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5198,23 +6380,34 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>-0.06560000000000001</v>
+        <v>0.1636</v>
       </c>
       <c r="D119" t="n">
-        <v>-0.1958</v>
+        <v>0.0914</v>
       </c>
       <c r="E119" t="n">
-        <v>-0.1297</v>
-      </c>
-      <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr"/>
-      <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr"/>
+        <v>-0.0015</v>
+      </c>
+      <c r="F119" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="G119" t="n">
+        <v>47301.1211</v>
+      </c>
+      <c r="H119" t="n">
+        <v>4.5387</v>
+      </c>
+      <c r="I119" t="n">
+        <v>66.015</v>
+      </c>
+      <c r="J119" t="n">
+        <v>118.3604</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>mc_111</t>
+          <t>mc_109</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5223,23 +6416,34 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>0.0372</v>
+        <v>0.1089</v>
       </c>
       <c r="D120" t="n">
-        <v>0.1398</v>
+        <v>-0.169</v>
       </c>
       <c r="E120" t="n">
-        <v>-0.0978</v>
-      </c>
-      <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr"/>
-      <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr"/>
+        <v>-0.016</v>
+      </c>
+      <c r="F120" t="n">
+        <v>-0.1509</v>
+      </c>
+      <c r="G120" t="n">
+        <v>39801.7344</v>
+      </c>
+      <c r="H120" t="n">
+        <v>4.2593</v>
+      </c>
+      <c r="I120" t="n">
+        <v>52.8308</v>
+      </c>
+      <c r="J120" t="n">
+        <v>127.5391</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>mc_112</t>
+          <t>mc_110</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5248,23 +6452,34 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>-0.1115</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="D121" t="n">
-        <v>-0.09470000000000001</v>
+        <v>-0.1958</v>
       </c>
       <c r="E121" t="n">
-        <v>-0.1019</v>
-      </c>
-      <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr"/>
-      <c r="H121" t="inlineStr"/>
-      <c r="I121" t="inlineStr"/>
+        <v>-0.1297</v>
+      </c>
+      <c r="F121" t="n">
+        <v>-0.1287</v>
+      </c>
+      <c r="G121" t="n">
+        <v>40460.0078</v>
+      </c>
+      <c r="H121" t="n">
+        <v>4.2067</v>
+      </c>
+      <c r="I121" t="n">
+        <v>53.1307</v>
+      </c>
+      <c r="J121" t="n">
+        <v>129.4054</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>mc_113</t>
+          <t>mc_111</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5273,23 +6488,34 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>0.1182</v>
+        <v>0.0372</v>
       </c>
       <c r="D122" t="n">
-        <v>0.1338</v>
+        <v>0.1398</v>
       </c>
       <c r="E122" t="n">
-        <v>0.0459</v>
-      </c>
-      <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr"/>
-      <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr"/>
+        <v>-0.0978</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.0226</v>
+      </c>
+      <c r="G122" t="n">
+        <v>50034.5586</v>
+      </c>
+      <c r="H122" t="n">
+        <v>4.6125</v>
+      </c>
+      <c r="I122" t="n">
+        <v>71.0865</v>
+      </c>
+      <c r="J122" t="n">
+        <v>118.6633</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>mc_114</t>
+          <t>mc_112</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5298,23 +6524,34 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>0.1386</v>
+        <v>-0.1115</v>
       </c>
       <c r="D123" t="n">
-        <v>-0.1575</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="E123" t="n">
-        <v>-0.0839</v>
-      </c>
-      <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr"/>
-      <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr"/>
+        <v>-0.1019</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.0475</v>
+      </c>
+      <c r="G123" t="n">
+        <v>50440.6211</v>
+      </c>
+      <c r="H123" t="n">
+        <v>4.6998</v>
+      </c>
+      <c r="I123" t="n">
+        <v>69.9982</v>
+      </c>
+      <c r="J123" t="n">
+        <v>128.1725</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>mc_115</t>
+          <t>mc_113</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5323,23 +6560,34 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>0.1555</v>
+        <v>0.1182</v>
       </c>
       <c r="D124" t="n">
-        <v>-0.1654</v>
+        <v>0.1338</v>
       </c>
       <c r="E124" t="n">
-        <v>0.064</v>
-      </c>
-      <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr"/>
-      <c r="H124" t="inlineStr"/>
-      <c r="I124" t="inlineStr"/>
+        <v>0.0459</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.1209</v>
+      </c>
+      <c r="G124" t="n">
+        <v>56079.418</v>
+      </c>
+      <c r="H124" t="n">
+        <v>4.8746</v>
+      </c>
+      <c r="I124" t="n">
+        <v>82.36369999999999</v>
+      </c>
+      <c r="J124" t="n">
+        <v>120.4822</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>mc_116</t>
+          <t>mc_114</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5348,23 +6596,34 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>0.145</v>
+        <v>0.1386</v>
       </c>
       <c r="D125" t="n">
-        <v>0.1953</v>
+        <v>-0.1575</v>
       </c>
       <c r="E125" t="n">
-        <v>0.1125</v>
-      </c>
-      <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr"/>
-      <c r="H125" t="inlineStr"/>
-      <c r="I125" t="inlineStr"/>
+        <v>-0.0839</v>
+      </c>
+      <c r="F125" t="n">
+        <v>-0.0507</v>
+      </c>
+      <c r="G125" t="n">
+        <v>46827.7969</v>
+      </c>
+      <c r="H125" t="n">
+        <v>5.1427</v>
+      </c>
+      <c r="I125" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="J125" t="n">
+        <v>119.7134</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>mc_117</t>
+          <t>mc_115</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5373,23 +6632,34 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>0.013</v>
+        <v>0.1555</v>
       </c>
       <c r="D126" t="n">
-        <v>0.1913</v>
+        <v>-0.1654</v>
       </c>
       <c r="E126" t="n">
-        <v>-0.067</v>
-      </c>
-      <c r="F126" t="inlineStr"/>
-      <c r="G126" t="inlineStr"/>
-      <c r="H126" t="inlineStr"/>
-      <c r="I126" t="inlineStr"/>
+        <v>0.064</v>
+      </c>
+      <c r="F126" t="n">
+        <v>-0.0143</v>
+      </c>
+      <c r="G126" t="n">
+        <v>47664.3047</v>
+      </c>
+      <c r="H126" t="n">
+        <v>4.7051</v>
+      </c>
+      <c r="I126" t="n">
+        <v>66.8146</v>
+      </c>
+      <c r="J126" t="n">
+        <v>118.679</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>mc_118</t>
+          <t>mc_116</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5398,23 +6668,34 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>-0.1861</v>
+        <v>0.145</v>
       </c>
       <c r="D127" t="n">
-        <v>0.1555</v>
+        <v>0.1953</v>
       </c>
       <c r="E127" t="n">
-        <v>-0.1271</v>
-      </c>
-      <c r="F127" t="inlineStr"/>
-      <c r="G127" t="inlineStr"/>
-      <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr"/>
+        <v>0.1125</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.1259</v>
+      </c>
+      <c r="G127" t="n">
+        <v>55193.5938</v>
+      </c>
+      <c r="H127" t="n">
+        <v>4.6885</v>
+      </c>
+      <c r="I127" t="n">
+        <v>79.8814</v>
+      </c>
+      <c r="J127" t="n">
+        <v>117.0417</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>mc_119</t>
+          <t>mc_117</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5423,23 +6704,34 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>-0.059</v>
+        <v>0.013</v>
       </c>
       <c r="D128" t="n">
-        <v>0.1289</v>
+        <v>0.1913</v>
       </c>
       <c r="E128" t="n">
-        <v>-0.1246</v>
-      </c>
-      <c r="F128" t="inlineStr"/>
-      <c r="G128" t="inlineStr"/>
-      <c r="H128" t="inlineStr"/>
-      <c r="I128" t="inlineStr"/>
+        <v>-0.067</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.0113</v>
+      </c>
+      <c r="G128" t="n">
+        <v>49513.5625</v>
+      </c>
+      <c r="H128" t="n">
+        <v>4.6625</v>
+      </c>
+      <c r="I128" t="n">
+        <v>70.21559999999999</v>
+      </c>
+      <c r="J128" t="n">
+        <v>116.8462</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>mc_120</t>
+          <t>mc_118</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5448,23 +6740,34 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>-0.0892</v>
+        <v>-0.1861</v>
       </c>
       <c r="D129" t="n">
-        <v>0.1919</v>
+        <v>0.1555</v>
       </c>
       <c r="E129" t="n">
-        <v>0.0513</v>
-      </c>
-      <c r="F129" t="inlineStr"/>
-      <c r="G129" t="inlineStr"/>
-      <c r="H129" t="inlineStr"/>
-      <c r="I129" t="inlineStr"/>
+        <v>-0.1271</v>
+      </c>
+      <c r="F129" t="n">
+        <v>-0.0294</v>
+      </c>
+      <c r="G129" t="n">
+        <v>46988.0742</v>
+      </c>
+      <c r="H129" t="n">
+        <v>4.6223</v>
+      </c>
+      <c r="I129" t="n">
+        <v>65.81610000000001</v>
+      </c>
+      <c r="J129" t="n">
+        <v>124.1089</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>mc_121</t>
+          <t>mc_119</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5473,1968 +6776,29 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>0.0658</v>
+        <v>-0.059</v>
       </c>
       <c r="D130" t="n">
-        <v>-0.1593</v>
+        <v>0.1289</v>
       </c>
       <c r="E130" t="n">
-        <v>-0.0832</v>
-      </c>
-      <c r="F130" t="inlineStr"/>
-      <c r="G130" t="inlineStr"/>
-      <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="1" t="inlineStr">
-        <is>
-          <t>mc_122</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C131" t="n">
-        <v>-0.0256</v>
-      </c>
-      <c r="D131" t="n">
-        <v>-0.0867</v>
-      </c>
-      <c r="E131" t="n">
-        <v>0.1082</v>
-      </c>
-      <c r="F131" t="inlineStr"/>
-      <c r="G131" t="inlineStr"/>
-      <c r="H131" t="inlineStr"/>
-      <c r="I131" t="inlineStr"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="1" t="inlineStr">
-        <is>
-          <t>mc_123</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C132" t="n">
-        <v>-0.1568</v>
-      </c>
-      <c r="D132" t="n">
-        <v>0.049</v>
-      </c>
-      <c r="E132" t="n">
-        <v>-0.1207</v>
-      </c>
-      <c r="F132" t="inlineStr"/>
-      <c r="G132" t="inlineStr"/>
-      <c r="H132" t="inlineStr"/>
-      <c r="I132" t="inlineStr"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="1" t="inlineStr">
-        <is>
-          <t>mc_124</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C133" t="n">
-        <v>-0.1845</v>
-      </c>
-      <c r="D133" t="n">
-        <v>-0.0042</v>
-      </c>
-      <c r="E133" t="n">
-        <v>0.1494</v>
-      </c>
-      <c r="F133" t="inlineStr"/>
-      <c r="G133" t="inlineStr"/>
-      <c r="H133" t="inlineStr"/>
-      <c r="I133" t="inlineStr"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="1" t="inlineStr">
-        <is>
-          <t>mc_125</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C134" t="n">
-        <v>-0.1257</v>
-      </c>
-      <c r="D134" t="n">
-        <v>-0.063</v>
-      </c>
-      <c r="E134" t="n">
-        <v>-0.0944</v>
-      </c>
-      <c r="F134" t="inlineStr"/>
-      <c r="G134" t="inlineStr"/>
-      <c r="H134" t="inlineStr"/>
-      <c r="I134" t="inlineStr"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="1" t="inlineStr">
-        <is>
-          <t>mc_126</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C135" t="n">
-        <v>-0.0672</v>
-      </c>
-      <c r="D135" t="n">
-        <v>-0.1617</v>
-      </c>
-      <c r="E135" t="n">
-        <v>-0.0249</v>
-      </c>
-      <c r="F135" t="inlineStr"/>
-      <c r="G135" t="inlineStr"/>
-      <c r="H135" t="inlineStr"/>
-      <c r="I135" t="inlineStr"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="1" t="inlineStr">
-        <is>
-          <t>mc_127</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C136" t="n">
-        <v>0.0871</v>
-      </c>
-      <c r="D136" t="n">
-        <v>-0.0344</v>
-      </c>
-      <c r="E136" t="n">
-        <v>-0.0305</v>
-      </c>
-      <c r="F136" t="inlineStr"/>
-      <c r="G136" t="inlineStr"/>
-      <c r="H136" t="inlineStr"/>
-      <c r="I136" t="inlineStr"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="1" t="inlineStr">
-        <is>
-          <t>mc_128</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C137" t="n">
-        <v>0.0641</v>
-      </c>
-      <c r="D137" t="n">
-        <v>0.0289</v>
-      </c>
-      <c r="E137" t="n">
-        <v>0.0334</v>
-      </c>
-      <c r="F137" t="inlineStr"/>
-      <c r="G137" t="inlineStr"/>
-      <c r="H137" t="inlineStr"/>
-      <c r="I137" t="inlineStr"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="1" t="inlineStr">
-        <is>
-          <t>mc_129</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C138" t="n">
-        <v>0.0926</v>
-      </c>
-      <c r="D138" t="n">
-        <v>0.0553</v>
-      </c>
-      <c r="E138" t="n">
-        <v>0.0842</v>
-      </c>
-      <c r="F138" t="inlineStr"/>
-      <c r="G138" t="inlineStr"/>
-      <c r="H138" t="inlineStr"/>
-      <c r="I138" t="inlineStr"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="1" t="inlineStr">
-        <is>
-          <t>mc_130</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C139" t="n">
-        <v>-0.0363</v>
-      </c>
-      <c r="D139" t="n">
-        <v>0.1431</v>
-      </c>
-      <c r="E139" t="n">
-        <v>0.0136</v>
-      </c>
-      <c r="F139" t="inlineStr"/>
-      <c r="G139" t="inlineStr"/>
-      <c r="H139" t="inlineStr"/>
-      <c r="I139" t="inlineStr"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="1" t="inlineStr">
-        <is>
-          <t>mc_131</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C140" t="n">
-        <v>-0.1434</v>
-      </c>
-      <c r="D140" t="n">
-        <v>0.0307</v>
-      </c>
-      <c r="E140" t="n">
-        <v>0.0706</v>
-      </c>
-      <c r="F140" t="inlineStr"/>
-      <c r="G140" t="inlineStr"/>
-      <c r="H140" t="inlineStr"/>
-      <c r="I140" t="inlineStr"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="1" t="inlineStr">
-        <is>
-          <t>mc_132</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C141" t="n">
-        <v>-0.1999</v>
-      </c>
-      <c r="D141" t="n">
-        <v>0.1544</v>
-      </c>
-      <c r="E141" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="F141" t="inlineStr"/>
-      <c r="G141" t="inlineStr"/>
-      <c r="H141" t="inlineStr"/>
-      <c r="I141" t="inlineStr"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="1" t="inlineStr">
-        <is>
-          <t>mc_133</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C142" t="n">
-        <v>0.1761</v>
-      </c>
-      <c r="D142" t="n">
-        <v>0.1814</v>
-      </c>
-      <c r="E142" t="n">
-        <v>0.0048</v>
-      </c>
-      <c r="F142" t="inlineStr"/>
-      <c r="G142" t="inlineStr"/>
-      <c r="H142" t="inlineStr"/>
-      <c r="I142" t="inlineStr"/>
-    </row>
-    <row r="143">
-      <c r="A143" s="1" t="inlineStr">
-        <is>
-          <t>mc_134</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C143" t="n">
-        <v>-0.09660000000000001</v>
-      </c>
-      <c r="D143" t="n">
-        <v>-0.0985</v>
-      </c>
-      <c r="E143" t="n">
-        <v>-0.1056</v>
-      </c>
-      <c r="F143" t="inlineStr"/>
-      <c r="G143" t="inlineStr"/>
-      <c r="H143" t="inlineStr"/>
-      <c r="I143" t="inlineStr"/>
-    </row>
-    <row r="144">
-      <c r="A144" s="1" t="inlineStr">
-        <is>
-          <t>mc_135</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C144" t="n">
-        <v>-0.0525</v>
-      </c>
-      <c r="D144" t="n">
-        <v>0.0025</v>
-      </c>
-      <c r="E144" t="n">
-        <v>0.09909999999999999</v>
-      </c>
-      <c r="F144" t="inlineStr"/>
-      <c r="G144" t="inlineStr"/>
-      <c r="H144" t="inlineStr"/>
-      <c r="I144" t="inlineStr"/>
-    </row>
-    <row r="145">
-      <c r="A145" s="1" t="inlineStr">
-        <is>
-          <t>mc_136</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C145" t="n">
-        <v>0.0334</v>
-      </c>
-      <c r="D145" t="n">
-        <v>0.0635</v>
-      </c>
-      <c r="E145" t="n">
-        <v>-0.1353</v>
-      </c>
-      <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr"/>
-      <c r="H145" t="inlineStr"/>
-      <c r="I145" t="inlineStr"/>
-    </row>
-    <row r="146">
-      <c r="A146" s="1" t="inlineStr">
-        <is>
-          <t>mc_137</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C146" t="n">
-        <v>0.0129</v>
-      </c>
-      <c r="D146" t="n">
-        <v>-0.0129</v>
-      </c>
-      <c r="E146" t="n">
-        <v>-0.1396</v>
-      </c>
-      <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr"/>
-      <c r="H146" t="inlineStr"/>
-      <c r="I146" t="inlineStr"/>
-    </row>
-    <row r="147">
-      <c r="A147" s="1" t="inlineStr">
-        <is>
-          <t>mc_138</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C147" t="n">
-        <v>-0.0116</v>
-      </c>
-      <c r="D147" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="E147" t="n">
-        <v>0.0813</v>
-      </c>
-      <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr"/>
-      <c r="H147" t="inlineStr"/>
-      <c r="I147" t="inlineStr"/>
-    </row>
-    <row r="148">
-      <c r="A148" s="1" t="inlineStr">
-        <is>
-          <t>mc_139</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C148" t="n">
-        <v>-0.1481</v>
-      </c>
-      <c r="D148" t="n">
-        <v>-0.0296</v>
-      </c>
-      <c r="E148" t="n">
-        <v>0.1373</v>
-      </c>
-      <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr"/>
-      <c r="H148" t="inlineStr"/>
-      <c r="I148" t="inlineStr"/>
-    </row>
-    <row r="149">
-      <c r="A149" s="1" t="inlineStr">
-        <is>
-          <t>mc_140</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C149" t="n">
-        <v>0.1563</v>
-      </c>
-      <c r="D149" t="n">
-        <v>-0.0516</v>
-      </c>
-      <c r="E149" t="n">
-        <v>-0.0735</v>
-      </c>
-      <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr"/>
-      <c r="H149" t="inlineStr"/>
-      <c r="I149" t="inlineStr"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="1" t="inlineStr">
-        <is>
-          <t>mc_141</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C150" t="n">
-        <v>0.07340000000000001</v>
-      </c>
-      <c r="D150" t="n">
-        <v>0.1134</v>
-      </c>
-      <c r="E150" t="n">
-        <v>-0.0895</v>
-      </c>
-      <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr"/>
-      <c r="H150" t="inlineStr"/>
-      <c r="I150" t="inlineStr"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="1" t="inlineStr">
-        <is>
-          <t>mc_142</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C151" t="n">
-        <v>-0.1718</v>
-      </c>
-      <c r="D151" t="n">
-        <v>0.1004</v>
-      </c>
-      <c r="E151" t="n">
-        <v>-0.1492</v>
-      </c>
-      <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr"/>
-      <c r="H151" t="inlineStr"/>
-      <c r="I151" t="inlineStr"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="1" t="inlineStr">
-        <is>
-          <t>mc_143</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C152" t="n">
-        <v>0.1401</v>
-      </c>
-      <c r="D152" t="n">
-        <v>-0.0911</v>
-      </c>
-      <c r="E152" t="n">
-        <v>0.0454</v>
-      </c>
-      <c r="F152" t="inlineStr"/>
-      <c r="G152" t="inlineStr"/>
-      <c r="H152" t="inlineStr"/>
-      <c r="I152" t="inlineStr"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="1" t="inlineStr">
-        <is>
-          <t>mc_144</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C153" t="n">
-        <v>-0.137</v>
-      </c>
-      <c r="D153" t="n">
-        <v>0.07870000000000001</v>
-      </c>
-      <c r="E153" t="n">
-        <v>0.09180000000000001</v>
-      </c>
-      <c r="F153" t="inlineStr"/>
-      <c r="G153" t="inlineStr"/>
-      <c r="H153" t="inlineStr"/>
-      <c r="I153" t="inlineStr"/>
-    </row>
-    <row r="154">
-      <c r="A154" s="1" t="inlineStr">
-        <is>
-          <t>mc_145</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C154" t="n">
-        <v>0.1014</v>
-      </c>
-      <c r="D154" t="n">
-        <v>-0.1483</v>
-      </c>
-      <c r="E154" t="n">
-        <v>-0.0202</v>
-      </c>
-      <c r="F154" t="inlineStr"/>
-      <c r="G154" t="inlineStr"/>
-      <c r="H154" t="inlineStr"/>
-      <c r="I154" t="inlineStr"/>
-    </row>
-    <row r="155">
-      <c r="A155" s="1" t="inlineStr">
-        <is>
-          <t>mc_146</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C155" t="n">
-        <v>0.1548</v>
-      </c>
-      <c r="D155" t="n">
-        <v>0.0692</v>
-      </c>
-      <c r="E155" t="n">
-        <v>0.1122</v>
-      </c>
-      <c r="F155" t="inlineStr"/>
-      <c r="G155" t="inlineStr"/>
-      <c r="H155" t="inlineStr"/>
-      <c r="I155" t="inlineStr"/>
-    </row>
-    <row r="156">
-      <c r="A156" s="1" t="inlineStr">
-        <is>
-          <t>mc_147</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C156" t="n">
-        <v>-0.0343</v>
-      </c>
-      <c r="D156" t="n">
-        <v>0.1739</v>
-      </c>
-      <c r="E156" t="n">
-        <v>-0.1197</v>
-      </c>
-      <c r="F156" t="inlineStr"/>
-      <c r="G156" t="inlineStr"/>
-      <c r="H156" t="inlineStr"/>
-      <c r="I156" t="inlineStr"/>
-    </row>
-    <row r="157">
-      <c r="A157" s="1" t="inlineStr">
-        <is>
-          <t>mc_148</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C157" t="n">
-        <v>0.1626</v>
-      </c>
-      <c r="D157" t="n">
-        <v>0.09320000000000001</v>
-      </c>
-      <c r="E157" t="n">
-        <v>-0.0443</v>
-      </c>
-      <c r="F157" t="inlineStr"/>
-      <c r="G157" t="inlineStr"/>
-      <c r="H157" t="inlineStr"/>
-      <c r="I157" t="inlineStr"/>
-    </row>
-    <row r="158">
-      <c r="A158" s="1" t="inlineStr">
-        <is>
-          <t>mc_149</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C158" t="n">
-        <v>-0.1132</v>
-      </c>
-      <c r="D158" t="n">
-        <v>0.169</v>
-      </c>
-      <c r="E158" t="n">
-        <v>0.0886</v>
-      </c>
-      <c r="F158" t="inlineStr"/>
-      <c r="G158" t="inlineStr"/>
-      <c r="H158" t="inlineStr"/>
-      <c r="I158" t="inlineStr"/>
-    </row>
-    <row r="159">
-      <c r="A159" s="1" t="inlineStr">
-        <is>
-          <t>mc_150</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C159" t="n">
-        <v>0.1127</v>
-      </c>
-      <c r="D159" t="n">
-        <v>0.0165</v>
-      </c>
-      <c r="E159" t="n">
-        <v>-0.128</v>
-      </c>
-      <c r="F159" t="inlineStr"/>
-      <c r="G159" t="inlineStr"/>
-      <c r="H159" t="inlineStr"/>
-      <c r="I159" t="inlineStr"/>
-    </row>
-    <row r="160">
-      <c r="A160" s="1" t="inlineStr">
-        <is>
-          <t>mc_151</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C160" t="n">
-        <v>0.1187</v>
-      </c>
-      <c r="D160" t="n">
-        <v>0.178</v>
-      </c>
-      <c r="E160" t="n">
-        <v>-0.1259</v>
-      </c>
-      <c r="F160" t="inlineStr"/>
-      <c r="G160" t="inlineStr"/>
-      <c r="H160" t="inlineStr"/>
-      <c r="I160" t="inlineStr"/>
-    </row>
-    <row r="161">
-      <c r="A161" s="1" t="inlineStr">
-        <is>
-          <t>mc_152</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C161" t="n">
-        <v>-0.046</v>
-      </c>
-      <c r="D161" t="n">
-        <v>-0.07439999999999999</v>
-      </c>
-      <c r="E161" t="n">
-        <v>0.0586</v>
-      </c>
-      <c r="F161" t="inlineStr"/>
-      <c r="G161" t="inlineStr"/>
-      <c r="H161" t="inlineStr"/>
-      <c r="I161" t="inlineStr"/>
-    </row>
-    <row r="162">
-      <c r="A162" s="1" t="inlineStr">
-        <is>
-          <t>mc_153</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C162" t="n">
-        <v>-0.09370000000000001</v>
-      </c>
-      <c r="D162" t="n">
-        <v>-0.128</v>
-      </c>
-      <c r="E162" t="n">
-        <v>-0.146</v>
-      </c>
-      <c r="F162" t="inlineStr"/>
-      <c r="G162" t="inlineStr"/>
-      <c r="H162" t="inlineStr"/>
-      <c r="I162" t="inlineStr"/>
-    </row>
-    <row r="163">
-      <c r="A163" s="1" t="inlineStr">
-        <is>
-          <t>mc_154</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C163" t="n">
-        <v>0.1229</v>
-      </c>
-      <c r="D163" t="n">
-        <v>-0.1798</v>
-      </c>
-      <c r="E163" t="n">
-        <v>0.1349</v>
-      </c>
-      <c r="F163" t="inlineStr"/>
-      <c r="G163" t="inlineStr"/>
-      <c r="H163" t="inlineStr"/>
-      <c r="I163" t="inlineStr"/>
-    </row>
-    <row r="164">
-      <c r="A164" s="1" t="inlineStr">
-        <is>
-          <t>mc_155</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C164" t="n">
-        <v>0.0586</v>
-      </c>
-      <c r="D164" t="n">
-        <v>0.008200000000000001</v>
-      </c>
-      <c r="E164" t="n">
-        <v>-0.0934</v>
-      </c>
-      <c r="F164" t="inlineStr"/>
-      <c r="G164" t="inlineStr"/>
-      <c r="H164" t="inlineStr"/>
-      <c r="I164" t="inlineStr"/>
-    </row>
-    <row r="165">
-      <c r="A165" s="1" t="inlineStr">
-        <is>
-          <t>mc_156</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C165" t="n">
-        <v>0.0033</v>
-      </c>
-      <c r="D165" t="n">
-        <v>0.0974</v>
-      </c>
-      <c r="E165" t="n">
-        <v>-0.0384</v>
-      </c>
-      <c r="F165" t="inlineStr"/>
-      <c r="G165" t="inlineStr"/>
-      <c r="H165" t="inlineStr"/>
-      <c r="I165" t="inlineStr"/>
-    </row>
-    <row r="166">
-      <c r="A166" s="1" t="inlineStr">
-        <is>
-          <t>mc_157</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C166" t="n">
-        <v>-0.1602</v>
-      </c>
-      <c r="D166" t="n">
-        <v>-0.1053</v>
-      </c>
-      <c r="E166" t="n">
-        <v>0.09719999999999999</v>
-      </c>
-      <c r="F166" t="inlineStr"/>
-      <c r="G166" t="inlineStr"/>
-      <c r="H166" t="inlineStr"/>
-      <c r="I166" t="inlineStr"/>
-    </row>
-    <row r="167">
-      <c r="A167" s="1" t="inlineStr">
-        <is>
-          <t>mc_158</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C167" t="n">
-        <v>-0.0221</v>
-      </c>
-      <c r="D167" t="n">
-        <v>0.1199</v>
-      </c>
-      <c r="E167" t="n">
-        <v>-0.0796</v>
-      </c>
-      <c r="F167" t="inlineStr"/>
-      <c r="G167" t="inlineStr"/>
-      <c r="H167" t="inlineStr"/>
-      <c r="I167" t="inlineStr"/>
-    </row>
-    <row r="168">
-      <c r="A168" s="1" t="inlineStr">
-        <is>
-          <t>mc_159</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C168" t="n">
-        <v>-0.1316</v>
-      </c>
-      <c r="D168" t="n">
-        <v>0.1295</v>
-      </c>
-      <c r="E168" t="n">
-        <v>0.0365</v>
-      </c>
-      <c r="F168" t="inlineStr"/>
-      <c r="G168" t="inlineStr"/>
-      <c r="H168" t="inlineStr"/>
-      <c r="I168" t="inlineStr"/>
-    </row>
-    <row r="169">
-      <c r="A169" s="1" t="inlineStr">
-        <is>
-          <t>mc_160</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C169" t="n">
-        <v>0.1051</v>
-      </c>
-      <c r="D169" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="E169" t="n">
-        <v>0.1258</v>
-      </c>
-      <c r="F169" t="inlineStr"/>
-      <c r="G169" t="inlineStr"/>
-      <c r="H169" t="inlineStr"/>
-      <c r="I169" t="inlineStr"/>
-    </row>
-    <row r="170">
-      <c r="A170" s="1" t="inlineStr">
-        <is>
-          <t>mc_161</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C170" t="n">
-        <v>0.1857</v>
-      </c>
-      <c r="D170" t="n">
-        <v>0.1968</v>
-      </c>
-      <c r="E170" t="n">
-        <v>-0.017</v>
-      </c>
-      <c r="F170" t="inlineStr"/>
-      <c r="G170" t="inlineStr"/>
-      <c r="H170" t="inlineStr"/>
-      <c r="I170" t="inlineStr"/>
-    </row>
-    <row r="171">
-      <c r="A171" s="1" t="inlineStr">
-        <is>
-          <t>mc_162</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C171" t="n">
-        <v>0.1661</v>
-      </c>
-      <c r="D171" t="n">
-        <v>-0.1219</v>
-      </c>
-      <c r="E171" t="n">
-        <v>-0.0348</v>
-      </c>
-      <c r="F171" t="inlineStr"/>
-      <c r="G171" t="inlineStr"/>
-      <c r="H171" t="inlineStr"/>
-      <c r="I171" t="inlineStr"/>
-    </row>
-    <row r="172">
-      <c r="A172" s="1" t="inlineStr">
-        <is>
-          <t>mc_163</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C172" t="n">
-        <v>0.0169</v>
-      </c>
-      <c r="D172" t="n">
-        <v>0.1632</v>
-      </c>
-      <c r="E172" t="n">
-        <v>0.0419</v>
-      </c>
-      <c r="F172" t="inlineStr"/>
-      <c r="G172" t="inlineStr"/>
-      <c r="H172" t="inlineStr"/>
-      <c r="I172" t="inlineStr"/>
-    </row>
-    <row r="173">
-      <c r="A173" s="1" t="inlineStr">
-        <is>
-          <t>mc_164</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C173" t="n">
-        <v>0.0761</v>
-      </c>
-      <c r="D173" t="n">
-        <v>-0.1871</v>
-      </c>
-      <c r="E173" t="n">
-        <v>0.1433</v>
-      </c>
-      <c r="F173" t="inlineStr"/>
-      <c r="G173" t="inlineStr"/>
-      <c r="H173" t="inlineStr"/>
-      <c r="I173" t="inlineStr"/>
-    </row>
-    <row r="174">
-      <c r="A174" s="1" t="inlineStr">
-        <is>
-          <t>mc_165</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C174" t="n">
-        <v>-0.0421</v>
-      </c>
-      <c r="D174" t="n">
-        <v>-0.1834</v>
-      </c>
-      <c r="E174" t="n">
-        <v>-0.1328</v>
-      </c>
-      <c r="F174" t="inlineStr"/>
-      <c r="G174" t="inlineStr"/>
-      <c r="H174" t="inlineStr"/>
-      <c r="I174" t="inlineStr"/>
-    </row>
-    <row r="175">
-      <c r="A175" s="1" t="inlineStr">
-        <is>
-          <t>mc_166</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C175" t="n">
-        <v>-0.0042</v>
-      </c>
-      <c r="D175" t="n">
-        <v>0.0227</v>
-      </c>
-      <c r="E175" t="n">
-        <v>0.1401</v>
-      </c>
-      <c r="F175" t="inlineStr"/>
-      <c r="G175" t="inlineStr"/>
-      <c r="H175" t="inlineStr"/>
-      <c r="I175" t="inlineStr"/>
-    </row>
-    <row r="176">
-      <c r="A176" s="1" t="inlineStr">
-        <is>
-          <t>mc_167</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C176" t="n">
-        <v>-0.1773</v>
-      </c>
-      <c r="D176" t="n">
-        <v>-0.1743</v>
-      </c>
-      <c r="E176" t="n">
-        <v>0.07530000000000001</v>
-      </c>
-      <c r="F176" t="inlineStr"/>
-      <c r="G176" t="inlineStr"/>
-      <c r="H176" t="inlineStr"/>
-      <c r="I176" t="inlineStr"/>
-    </row>
-    <row r="177">
-      <c r="A177" s="1" t="inlineStr">
-        <is>
-          <t>mc_168</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C177" t="n">
-        <v>0.0511</v>
-      </c>
-      <c r="D177" t="n">
-        <v>0.1319</v>
-      </c>
-      <c r="E177" t="n">
-        <v>0.0239</v>
-      </c>
-      <c r="F177" t="inlineStr"/>
-      <c r="G177" t="inlineStr"/>
-      <c r="H177" t="inlineStr"/>
-      <c r="I177" t="inlineStr"/>
-    </row>
-    <row r="178">
-      <c r="A178" s="1" t="inlineStr">
-        <is>
-          <t>mc_169</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C178" t="n">
-        <v>-0.0157</v>
-      </c>
-      <c r="D178" t="n">
-        <v>-0.1122</v>
-      </c>
-      <c r="E178" t="n">
-        <v>0.0733</v>
-      </c>
-      <c r="F178" t="inlineStr"/>
-      <c r="G178" t="inlineStr"/>
-      <c r="H178" t="inlineStr"/>
-      <c r="I178" t="inlineStr"/>
-    </row>
-    <row r="179">
-      <c r="A179" s="1" t="inlineStr">
-        <is>
-          <t>mc_170</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C179" t="n">
-        <v>-0.1199</v>
-      </c>
-      <c r="D179" t="n">
-        <v>-0.0806</v>
-      </c>
-      <c r="E179" t="n">
-        <v>-0.0675</v>
-      </c>
-      <c r="F179" t="inlineStr"/>
-      <c r="G179" t="inlineStr"/>
-      <c r="H179" t="inlineStr"/>
-      <c r="I179" t="inlineStr"/>
-    </row>
-    <row r="180">
-      <c r="A180" s="1" t="inlineStr">
-        <is>
-          <t>mc_171</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C180" t="n">
-        <v>-0.1698</v>
-      </c>
-      <c r="D180" t="n">
-        <v>-0.1305</v>
-      </c>
-      <c r="E180" t="n">
-        <v>-0.09810000000000001</v>
-      </c>
-      <c r="F180" t="inlineStr"/>
-      <c r="G180" t="inlineStr"/>
-      <c r="H180" t="inlineStr"/>
-      <c r="I180" t="inlineStr"/>
-    </row>
-    <row r="181">
-      <c r="A181" s="1" t="inlineStr">
-        <is>
-          <t>mc_172</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C181" t="n">
-        <v>0.0226</v>
-      </c>
-      <c r="D181" t="n">
-        <v>0.1358</v>
-      </c>
-      <c r="E181" t="n">
-        <v>0.0159</v>
-      </c>
-      <c r="F181" t="inlineStr"/>
-      <c r="G181" t="inlineStr"/>
-      <c r="H181" t="inlineStr"/>
-      <c r="I181" t="inlineStr"/>
-    </row>
-    <row r="182">
-      <c r="A182" s="1" t="inlineStr">
-        <is>
-          <t>mc_173</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C182" t="n">
-        <v>0.0956</v>
-      </c>
-      <c r="D182" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E182" t="n">
-        <v>-0.0555</v>
-      </c>
-      <c r="F182" t="inlineStr"/>
-      <c r="G182" t="inlineStr"/>
-      <c r="H182" t="inlineStr"/>
-      <c r="I182" t="inlineStr"/>
-    </row>
-    <row r="183">
-      <c r="A183" s="1" t="inlineStr">
-        <is>
-          <t>mc_174</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C183" t="n">
-        <v>0.1326</v>
-      </c>
-      <c r="D183" t="n">
-        <v>0.0396</v>
-      </c>
-      <c r="E183" t="n">
-        <v>0.1166</v>
-      </c>
-      <c r="F183" t="inlineStr"/>
-      <c r="G183" t="inlineStr"/>
-      <c r="H183" t="inlineStr"/>
-      <c r="I183" t="inlineStr"/>
-    </row>
-    <row r="184">
-      <c r="A184" s="1" t="inlineStr">
-        <is>
-          <t>mc_175</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C184" t="n">
-        <v>-0.1896</v>
-      </c>
-      <c r="D184" t="n">
-        <v>-0.0176</v>
-      </c>
-      <c r="E184" t="n">
-        <v>-0.008</v>
-      </c>
-      <c r="F184" t="inlineStr"/>
-      <c r="G184" t="inlineStr"/>
-      <c r="H184" t="inlineStr"/>
-      <c r="I184" t="inlineStr"/>
-    </row>
-    <row r="185">
-      <c r="A185" s="1" t="inlineStr">
-        <is>
-          <t>mc_176</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C185" t="n">
-        <v>-0.081</v>
-      </c>
-      <c r="D185" t="n">
-        <v>-0.1391</v>
-      </c>
-      <c r="E185" t="n">
-        <v>0.0408</v>
-      </c>
-      <c r="F185" t="inlineStr"/>
-      <c r="G185" t="inlineStr"/>
-      <c r="H185" t="inlineStr"/>
-      <c r="I185" t="inlineStr"/>
-    </row>
-    <row r="186">
-      <c r="A186" s="1" t="inlineStr">
-        <is>
-          <t>mc_177</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C186" t="n">
-        <v>-0.106</v>
-      </c>
-      <c r="D186" t="n">
-        <v>-0.0445</v>
-      </c>
-      <c r="E186" t="n">
-        <v>-0.0469</v>
-      </c>
-      <c r="F186" t="inlineStr"/>
-      <c r="G186" t="inlineStr"/>
-      <c r="H186" t="inlineStr"/>
-      <c r="I186" t="inlineStr"/>
-    </row>
-    <row r="187">
-      <c r="A187" s="1" t="inlineStr">
-        <is>
-          <t>mc_178</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C187" t="n">
-        <v>0.127</v>
-      </c>
-      <c r="D187" t="n">
-        <v>0.0505</v>
-      </c>
-      <c r="E187" t="n">
-        <v>-0.0011</v>
-      </c>
-      <c r="F187" t="inlineStr"/>
-      <c r="G187" t="inlineStr"/>
-      <c r="H187" t="inlineStr"/>
-      <c r="I187" t="inlineStr"/>
-    </row>
-    <row r="188">
-      <c r="A188" s="1" t="inlineStr">
-        <is>
-          <t>mc_179</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C188" t="n">
-        <v>0.191</v>
-      </c>
-      <c r="D188" t="n">
-        <v>-0.0081</v>
-      </c>
-      <c r="E188" t="n">
-        <v>0.1129</v>
-      </c>
-      <c r="F188" t="inlineStr"/>
-      <c r="G188" t="inlineStr"/>
-      <c r="H188" t="inlineStr"/>
-      <c r="I188" t="inlineStr"/>
-    </row>
-    <row r="189">
-      <c r="A189" s="1" t="inlineStr">
-        <is>
-          <t>mc_180</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C189" t="n">
-        <v>-0.008399999999999999</v>
-      </c>
-      <c r="D189" t="n">
-        <v>0.1086</v>
-      </c>
-      <c r="E189" t="n">
-        <v>0.0214</v>
-      </c>
-      <c r="F189" t="inlineStr"/>
-      <c r="G189" t="inlineStr"/>
-      <c r="H189" t="inlineStr"/>
-      <c r="I189" t="inlineStr"/>
-    </row>
-    <row r="190">
-      <c r="A190" s="1" t="inlineStr">
-        <is>
-          <t>mc_181</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C190" t="n">
-        <v>-0.1209</v>
-      </c>
-      <c r="D190" t="n">
-        <v>-0.1414</v>
-      </c>
-      <c r="E190" t="n">
-        <v>-0.0297</v>
-      </c>
-      <c r="F190" t="inlineStr"/>
-      <c r="G190" t="inlineStr"/>
-      <c r="H190" t="inlineStr"/>
-      <c r="I190" t="inlineStr"/>
-    </row>
-    <row r="191">
-      <c r="A191" s="1" t="inlineStr">
-        <is>
-          <t>mc_182</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C191" t="n">
-        <v>-0.079</v>
-      </c>
-      <c r="D191" t="n">
-        <v>0.0893</v>
-      </c>
-      <c r="E191" t="n">
-        <v>-0.0712</v>
-      </c>
-      <c r="F191" t="inlineStr"/>
-      <c r="G191" t="inlineStr"/>
-      <c r="H191" t="inlineStr"/>
-      <c r="I191" t="inlineStr"/>
-    </row>
-    <row r="192">
-      <c r="A192" s="1" t="inlineStr">
-        <is>
-          <t>mc_183</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C192" t="n">
-        <v>-0.1903</v>
-      </c>
-      <c r="D192" t="n">
-        <v>-0.1991</v>
-      </c>
-      <c r="E192" t="n">
-        <v>0.1217</v>
-      </c>
-      <c r="F192" t="inlineStr"/>
-      <c r="G192" t="inlineStr"/>
-      <c r="H192" t="inlineStr"/>
-      <c r="I192" t="inlineStr"/>
-    </row>
-    <row r="193">
-      <c r="A193" s="1" t="inlineStr">
-        <is>
-          <t>mc_184</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C193" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="D193" t="n">
-        <v>-0.1908</v>
-      </c>
-      <c r="E193" t="n">
-        <v>0.0285</v>
-      </c>
-      <c r="F193" t="inlineStr"/>
-      <c r="G193" t="inlineStr"/>
-      <c r="H193" t="inlineStr"/>
-      <c r="I193" t="inlineStr"/>
-    </row>
-    <row r="194">
-      <c r="A194" s="1" t="inlineStr">
-        <is>
-          <t>mc_185</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C194" t="n">
-        <v>0.1997</v>
-      </c>
-      <c r="D194" t="n">
-        <v>-0.0393</v>
-      </c>
-      <c r="E194" t="n">
-        <v>-0.1124</v>
-      </c>
-      <c r="F194" t="inlineStr"/>
-      <c r="G194" t="inlineStr"/>
-      <c r="H194" t="inlineStr"/>
-      <c r="I194" t="inlineStr"/>
-    </row>
-    <row r="195">
-      <c r="A195" s="1" t="inlineStr">
-        <is>
-          <t>mc_186</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C195" t="n">
-        <v>-0.1044</v>
-      </c>
-      <c r="D195" t="n">
-        <v>0.0412</v>
-      </c>
-      <c r="E195" t="n">
-        <v>-0.0606</v>
-      </c>
-      <c r="F195" t="inlineStr"/>
-      <c r="G195" t="inlineStr"/>
-      <c r="H195" t="inlineStr"/>
-      <c r="I195" t="inlineStr"/>
-    </row>
-    <row r="196">
-      <c r="A196" s="1" t="inlineStr">
-        <is>
-          <t>mc_187</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C196" t="n">
-        <v>0.1704</v>
-      </c>
-      <c r="D196" t="n">
-        <v>-0.1046</v>
-      </c>
-      <c r="E196" t="n">
-        <v>-0.07679999999999999</v>
-      </c>
-      <c r="F196" t="inlineStr"/>
-      <c r="G196" t="inlineStr"/>
-      <c r="H196" t="inlineStr"/>
-      <c r="I196" t="inlineStr"/>
-    </row>
-    <row r="197">
-      <c r="A197" s="1" t="inlineStr">
-        <is>
-          <t>mc_188</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C197" t="n">
-        <v>0.0803</v>
-      </c>
-      <c r="D197" t="n">
-        <v>-0.1153</v>
-      </c>
-      <c r="E197" t="n">
-        <v>-0.0501</v>
-      </c>
-      <c r="F197" t="inlineStr"/>
-      <c r="G197" t="inlineStr"/>
-      <c r="H197" t="inlineStr"/>
-      <c r="I197" t="inlineStr"/>
-    </row>
-    <row r="198">
-      <c r="A198" s="1" t="inlineStr">
-        <is>
-          <t>mc_189</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C198" t="n">
-        <v>-0.06419999999999999</v>
-      </c>
-      <c r="D198" t="n">
-        <v>-0.0223</v>
-      </c>
-      <c r="E198" t="n">
-        <v>-0.0133</v>
-      </c>
-      <c r="F198" t="inlineStr"/>
-      <c r="G198" t="inlineStr"/>
-      <c r="H198" t="inlineStr"/>
-      <c r="I198" t="inlineStr"/>
-    </row>
-    <row r="199">
-      <c r="A199" s="1" t="inlineStr">
-        <is>
-          <t>mc_190</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C199" t="n">
-        <v>0.1806</v>
-      </c>
-      <c r="D199" t="n">
-        <v>-0.1677</v>
-      </c>
-      <c r="E199" t="n">
-        <v>0.1278</v>
-      </c>
-      <c r="F199" t="inlineStr"/>
-      <c r="G199" t="inlineStr"/>
-      <c r="H199" t="inlineStr"/>
-      <c r="I199" t="inlineStr"/>
-    </row>
-    <row r="200">
-      <c r="A200" s="1" t="inlineStr">
-        <is>
-          <t>mc_191</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C200" t="n">
-        <v>0.0098</v>
-      </c>
-      <c r="D200" t="n">
-        <v>0.0732</v>
-      </c>
-      <c r="E200" t="n">
-        <v>-0.0055</v>
-      </c>
-      <c r="F200" t="inlineStr"/>
-      <c r="G200" t="inlineStr"/>
-      <c r="H200" t="inlineStr"/>
-      <c r="I200" t="inlineStr"/>
-    </row>
-    <row r="201">
-      <c r="A201" s="1" t="inlineStr">
-        <is>
-          <t>mc_192</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C201" t="n">
-        <v>0.1495</v>
-      </c>
-      <c r="D201" t="n">
-        <v>0.1493</v>
-      </c>
-      <c r="E201" t="n">
-        <v>0.064</v>
-      </c>
-      <c r="F201" t="inlineStr"/>
-      <c r="G201" t="inlineStr"/>
-      <c r="H201" t="inlineStr"/>
-      <c r="I201" t="inlineStr"/>
-    </row>
-    <row r="202">
-      <c r="A202" s="1" t="inlineStr">
-        <is>
-          <t>mc_193</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C202" t="n">
-        <v>-0.153</v>
-      </c>
-      <c r="D202" t="n">
-        <v>-0.06710000000000001</v>
-      </c>
-      <c r="E202" t="n">
-        <v>0.06270000000000001</v>
-      </c>
-      <c r="F202" t="inlineStr"/>
-      <c r="G202" t="inlineStr"/>
-      <c r="H202" t="inlineStr"/>
-      <c r="I202" t="inlineStr"/>
-    </row>
-    <row r="203">
-      <c r="A203" s="1" t="inlineStr">
-        <is>
-          <t>mc_194</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C203" t="n">
-        <v>0.0431</v>
-      </c>
-      <c r="D203" t="n">
-        <v>0.0805</v>
-      </c>
-      <c r="E203" t="n">
-        <v>0.0554</v>
-      </c>
-      <c r="F203" t="inlineStr"/>
-      <c r="G203" t="inlineStr"/>
-      <c r="H203" t="inlineStr"/>
-      <c r="I203" t="inlineStr"/>
-    </row>
-    <row r="204">
-      <c r="A204" s="1" t="inlineStr">
-        <is>
-          <t>mc_195</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C204" t="n">
-        <v>-0.0743</v>
-      </c>
-      <c r="D204" t="n">
-        <v>-0.057</v>
-      </c>
-      <c r="E204" t="n">
-        <v>0.0012</v>
-      </c>
-      <c r="F204" t="inlineStr"/>
-      <c r="G204" t="inlineStr"/>
-      <c r="H204" t="inlineStr"/>
-      <c r="I204" t="inlineStr"/>
-    </row>
-    <row r="205">
-      <c r="A205" s="1" t="inlineStr">
-        <is>
-          <t>mc_196</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C205" t="n">
-        <v>0.1397</v>
-      </c>
-      <c r="D205" t="n">
-        <v>-0.0751</v>
-      </c>
-      <c r="E205" t="n">
-        <v>0.104</v>
-      </c>
-      <c r="F205" t="inlineStr"/>
-      <c r="G205" t="inlineStr"/>
-      <c r="H205" t="inlineStr"/>
-      <c r="I205" t="inlineStr"/>
-    </row>
-    <row r="206">
-      <c r="A206" s="1" t="inlineStr">
-        <is>
-          <t>mc_197</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C206" t="n">
-        <v>0.0451</v>
-      </c>
-      <c r="D206" t="n">
-        <v>-0.0464</v>
-      </c>
-      <c r="E206" t="n">
-        <v>-0.1039</v>
-      </c>
-      <c r="F206" t="inlineStr"/>
-      <c r="G206" t="inlineStr"/>
-      <c r="H206" t="inlineStr"/>
-      <c r="I206" t="inlineStr"/>
-    </row>
-    <row r="207">
-      <c r="A207" s="1" t="inlineStr">
-        <is>
-          <t>mc_198</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C207" t="n">
-        <v>0.0386</v>
-      </c>
-      <c r="D207" t="n">
-        <v>0.1897</v>
-      </c>
-      <c r="E207" t="n">
-        <v>-0.0588</v>
-      </c>
-      <c r="F207" t="inlineStr"/>
-      <c r="G207" t="inlineStr"/>
-      <c r="H207" t="inlineStr"/>
-      <c r="I207" t="inlineStr"/>
-    </row>
-    <row r="208">
-      <c r="A208" s="1" t="inlineStr">
-        <is>
-          <t>mc_199</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>montecarlo</t>
-        </is>
-      </c>
-      <c r="C208" t="n">
-        <v>-0.0576</v>
-      </c>
-      <c r="D208" t="n">
-        <v>0.158</v>
-      </c>
-      <c r="E208" t="n">
-        <v>-0.1158</v>
-      </c>
-      <c r="F208" t="inlineStr"/>
-      <c r="G208" t="inlineStr"/>
-      <c r="H208" t="inlineStr"/>
-      <c r="I208" t="inlineStr"/>
+        <v>-0.1246</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.1648</v>
+      </c>
+      <c r="G130" t="n">
+        <v>55132.668</v>
+      </c>
+      <c r="H130" t="n">
+        <v>5.0223</v>
+      </c>
+      <c r="I130" t="n">
+        <v>77.68519999999999</v>
+      </c>
+      <c r="J130" t="n">
+        <v>123.4679</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7447,7 +6811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7500,16 +6864,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>47579.736</v>
+        <v>40574.267</v>
       </c>
       <c r="D2" t="n">
-        <v>49207.877</v>
+        <v>50057.26</v>
       </c>
       <c r="E2" t="n">
-        <v>49818.23</v>
+        <v>55938.459</v>
       </c>
       <c r="F2" t="n">
-        <v>0.729</v>
+        <v>4.749</v>
       </c>
     </row>
     <row r="3">
@@ -7522,16 +6886,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4.401</v>
+        <v>4.27</v>
       </c>
       <c r="D3" t="n">
-        <v>4.543</v>
+        <v>4.674</v>
       </c>
       <c r="E3" t="n">
-        <v>4.897</v>
+        <v>5.05</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.566</v>
+        <v>-0.556</v>
       </c>
     </row>
     <row r="4">
@@ -7544,16 +6908,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>64.581</v>
+        <v>53.395</v>
       </c>
       <c r="D4" t="n">
-        <v>69.407</v>
+        <v>70.727</v>
       </c>
       <c r="E4" t="n">
-        <v>71.024</v>
+        <v>80.88</v>
       </c>
       <c r="F4" t="n">
-        <v>1.125</v>
+        <v>5.852</v>
       </c>
     </row>
     <row r="5">
@@ -7566,16 +6930,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>117.061</v>
+        <v>116.026</v>
       </c>
       <c r="D5" t="n">
-        <v>119.166</v>
+        <v>121.788</v>
       </c>
       <c r="E5" t="n">
-        <v>124.959</v>
+        <v>128.789</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.201</v>
+        <v>-0.793</v>
       </c>
     </row>
     <row r="6">
@@ -7588,16 +6952,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>47297.484</v>
+        <v>41202.54</v>
       </c>
       <c r="D6" t="n">
-        <v>48851.789</v>
+        <v>49950.51</v>
       </c>
       <c r="E6" t="n">
-        <v>49585.391</v>
+        <v>55938.459</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>4.525</v>
       </c>
     </row>
     <row r="7">
@@ -7610,16 +6974,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4.48</v>
+        <v>4.27</v>
       </c>
       <c r="D7" t="n">
-        <v>4.635</v>
+        <v>4.807</v>
       </c>
       <c r="E7" t="n">
-        <v>4.945</v>
+        <v>5.153</v>
       </c>
       <c r="F7" t="n">
-        <v>0.442</v>
+        <v>2.283</v>
       </c>
     </row>
     <row r="8">
@@ -7632,16 +6996,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>64.34099999999999</v>
+        <v>55.135</v>
       </c>
       <c r="D8" t="n">
-        <v>68.687</v>
+        <v>70.727</v>
       </c>
       <c r="E8" t="n">
-        <v>70.691</v>
+        <v>80.88</v>
       </c>
       <c r="F8" t="n">
-        <v>0.076</v>
+        <v>5.852</v>
       </c>
     </row>
     <row r="9">
@@ -7654,16 +7018,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>116.773</v>
+        <v>116.586</v>
       </c>
       <c r="D9" t="n">
-        <v>119.166</v>
+        <v>120.366</v>
       </c>
       <c r="E9" t="n">
-        <v>126.234</v>
+        <v>128.789</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.201</v>
+        <v>-1.951</v>
       </c>
     </row>
     <row r="10">
@@ -7676,16 +7040,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>46839.582</v>
+        <v>40632.012</v>
       </c>
       <c r="D10" t="n">
-        <v>48851.789</v>
+        <v>49950.51</v>
       </c>
       <c r="E10" t="n">
-        <v>49585.391</v>
+        <v>55776.069</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>4.525</v>
       </c>
     </row>
     <row r="11">
@@ -7698,16 +7062,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4.454</v>
+        <v>4.27</v>
       </c>
       <c r="D11" t="n">
-        <v>4.624</v>
+        <v>4.863</v>
       </c>
       <c r="E11" t="n">
-        <v>4.897</v>
+        <v>5.291</v>
       </c>
       <c r="F11" t="n">
-        <v>0.197</v>
+        <v>3.473</v>
       </c>
     </row>
     <row r="12">
@@ -7720,16 +7084,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>64.08199999999999</v>
+        <v>53.528</v>
       </c>
       <c r="D12" t="n">
-        <v>68.687</v>
+        <v>70.727</v>
       </c>
       <c r="E12" t="n">
-        <v>70.535</v>
+        <v>80.637</v>
       </c>
       <c r="F12" t="n">
-        <v>0.076</v>
+        <v>5.852</v>
       </c>
     </row>
     <row r="13">
@@ -7742,21 +7106,21 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>116.816</v>
+        <v>116.586</v>
       </c>
       <c r="D13" t="n">
-        <v>119.827</v>
+        <v>120.258</v>
       </c>
       <c r="E13" t="n">
-        <v>126.234</v>
+        <v>128.657</v>
       </c>
       <c r="F13" t="n">
-        <v>0.353</v>
+        <v>-2.039</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -7764,21 +7128,21 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>46884.528</v>
+        <v>40710.442</v>
       </c>
       <c r="D14" t="n">
-        <v>48851.789</v>
+        <v>48943.879</v>
       </c>
       <c r="E14" t="n">
-        <v>49533.296</v>
+        <v>57039.196</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>2.419</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -7786,21 +7150,21 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4.419</v>
+        <v>4.27</v>
       </c>
       <c r="D15" t="n">
-        <v>4.615</v>
+        <v>4.742</v>
       </c>
       <c r="E15" t="n">
-        <v>4.859</v>
+        <v>5.266</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>0.902</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -7808,21 +7172,21 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>64.181</v>
+        <v>53.937</v>
       </c>
       <c r="D16" t="n">
-        <v>68.63500000000001</v>
+        <v>68.998</v>
       </c>
       <c r="E16" t="n">
-        <v>70.46299999999999</v>
+        <v>83.377</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>3.264</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -7830,15 +7194,279 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>116.788</v>
+        <v>116.762</v>
       </c>
       <c r="D17" t="n">
-        <v>119.406</v>
+        <v>120.623</v>
       </c>
       <c r="E17" t="n">
-        <v>125.783</v>
+        <v>129.019</v>
       </c>
       <c r="F17" t="n">
+        <v>-1.742</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>75</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Total transmission [km]</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>39517.768</v>
+      </c>
+      <c r="D18" t="n">
+        <v>47798.402</v>
+      </c>
+      <c r="E18" t="n">
+        <v>57004.205</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.022</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>75</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Total transmission capacity [GW]</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>4.216</v>
+      </c>
+      <c r="D19" t="n">
+        <v>4.576</v>
+      </c>
+      <c r="E19" t="n">
+        <v>5.275</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-2.649</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>75</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Total installed generation capacity [GW]</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>51.647</v>
+      </c>
+      <c r="D20" t="n">
+        <v>66.76000000000001</v>
+      </c>
+      <c r="E20" t="n">
+        <v>83.128</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-0.08599999999999999</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>75</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Country average electricity price [USD/MWh]</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>116.692</v>
+      </c>
+      <c r="D21" t="n">
+        <v>122.897</v>
+      </c>
+      <c r="E21" t="n">
+        <v>129.63</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>100</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Total transmission [km]</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>39265.192</v>
+      </c>
+      <c r="D22" t="n">
+        <v>47787.914</v>
+      </c>
+      <c r="E22" t="n">
+        <v>56948.894</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>100</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Total transmission capacity [GW]</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>4.224</v>
+      </c>
+      <c r="D23" t="n">
+        <v>4.701</v>
+      </c>
+      <c r="E23" t="n">
+        <v>5.365</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.023</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>100</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Total installed generation capacity [GW]</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>51.111</v>
+      </c>
+      <c r="D24" t="n">
+        <v>66.79000000000001</v>
+      </c>
+      <c r="E24" t="n">
+        <v>83.104</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-0.041</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>100</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Country average electricity price [USD/MWh]</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>116.762</v>
+      </c>
+      <c r="D25" t="n">
+        <v>122.83</v>
+      </c>
+      <c r="E25" t="n">
+        <v>129.583</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.056</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>120</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Total transmission [km]</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>39857.991</v>
+      </c>
+      <c r="D26" t="n">
+        <v>47787.914</v>
+      </c>
+      <c r="E26" t="n">
+        <v>57068.695</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>120</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Total transmission capacity [GW]</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>4.228</v>
+      </c>
+      <c r="D27" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E27" t="n">
+        <v>5.288</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>120</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Total installed generation capacity [GW]</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>52.33</v>
+      </c>
+      <c r="D28" t="n">
+        <v>66.81699999999999</v>
+      </c>
+      <c r="E28" t="n">
+        <v>82.49299999999999</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>120</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Country average electricity price [USD/MWh]</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>116.832</v>
+      </c>
+      <c r="D29" t="n">
+        <v>122.762</v>
+      </c>
+      <c r="E29" t="n">
+        <v>129.423</v>
+      </c>
+      <c r="F29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7853,7 +7481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -7893,16 +7521,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.129</v>
+        <v>0.044</v>
       </c>
       <c r="C2" t="n">
-        <v>0.222</v>
+        <v>0.081</v>
       </c>
       <c r="D2" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.053</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.5570000000000001</v>
+        <v>-0.264</v>
       </c>
     </row>
     <row r="3">
@@ -7912,16 +7540,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.047</v>
+        <v>0.112</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.468</v>
+        <v>-0.142</v>
       </c>
       <c r="D3" t="n">
-        <v>0.13</v>
+        <v>0.121</v>
       </c>
       <c r="E3" t="n">
-        <v>0.027</v>
+        <v>-0.081</v>
       </c>
     </row>
     <row r="4">
@@ -7931,16 +7559,35 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.359</v>
+        <v>-0.008</v>
       </c>
       <c r="C4" t="n">
-        <v>0.021</v>
+        <v>-0.013</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.421</v>
+        <v>-0.014</v>
       </c>
       <c r="E4" t="n">
-        <v>0.307</v>
+        <v>-0.014</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Demand growth</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.973</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.752</v>
       </c>
     </row>
   </sheetData>
